--- a/transfert.xlsx
+++ b/transfert.xlsx
@@ -9,13 +9,13 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="10710" windowHeight="4100"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15530" windowHeight="6930"/>
   </bookViews>
   <sheets>
     <sheet name="Données du dasboard" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Données du dasboard'!$A$1:$S$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Données du dasboard'!$A$1:$U$38</definedName>
     <definedName name="corbeil">#REF!</definedName>
     <definedName name="corbeilHeader">#REF!</definedName>
     <definedName name="en_tete">#REF!</definedName>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="798" uniqueCount="310">
   <si>
     <t>ID DOSSIER</t>
   </si>
@@ -53,9 +53,6 @@
     <t>TYPE OPERATION TM</t>
   </si>
   <si>
-    <t>SUPPORT INITIAL</t>
-  </si>
-  <si>
     <t>Type OFFRE</t>
   </si>
   <si>
@@ -86,18 +83,21 @@
     <t>DATE FIN</t>
   </si>
   <si>
+    <t>REFERENCE</t>
+  </si>
+  <si>
+    <t>CONTACT CLIENT</t>
+  </si>
+  <si>
+    <t>NDEM</t>
+  </si>
+  <si>
     <t>CARACTERISTIQUE</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>support</t>
-  </si>
-  <si>
-    <t>ftto</t>
-  </si>
-  <si>
     <t>fo</t>
   </si>
   <si>
@@ -146,6 +146,9 @@
     <t>2720316600</t>
   </si>
   <si>
+    <t>0707722441</t>
+  </si>
+  <si>
     <t>T2</t>
   </si>
   <si>
@@ -173,103 +176,133 @@
     <t>65533632</t>
   </si>
   <si>
+    <t>26/06/2026 14:30:26</t>
+  </si>
+  <si>
+    <t>65395686</t>
+  </si>
+  <si>
+    <t>24/06/2026 11:38:13</t>
+  </si>
+  <si>
+    <t>2720209800</t>
+  </si>
+  <si>
+    <t>65532878</t>
+  </si>
+  <si>
+    <t>26/06/2026 14:21:02</t>
+  </si>
+  <si>
+    <t>65400923</t>
+  </si>
+  <si>
+    <t>24/06/2026 12:37:44</t>
+  </si>
+  <si>
+    <t>BNI GESTION</t>
+  </si>
+  <si>
+    <t>SIEGE BNI PLATEAU</t>
+  </si>
+  <si>
+    <t>2720208110</t>
+  </si>
+  <si>
+    <t>T0</t>
+  </si>
+  <si>
+    <t>26/06/2026 14:59:53</t>
+  </si>
+  <si>
+    <t>65536408</t>
+  </si>
+  <si>
+    <t>65401420</t>
+  </si>
+  <si>
+    <t>24/06/2026 12:44:36</t>
+  </si>
+  <si>
+    <t>2720310777</t>
+  </si>
+  <si>
+    <t>65533279</t>
+  </si>
+  <si>
+    <t>26/06/2026 14:26:10</t>
+  </si>
+  <si>
+    <t>65402557</t>
+  </si>
+  <si>
+    <t>24/06/2026 12:58:18</t>
+  </si>
+  <si>
+    <t>2720312270</t>
+  </si>
+  <si>
+    <t>65536161</t>
+  </si>
+  <si>
+    <t>26/06/2026 14:55:41</t>
+  </si>
+  <si>
+    <t>65411444</t>
+  </si>
+  <si>
+    <t>24/06/2026 14:51:50</t>
+  </si>
+  <si>
+    <t>PLATEAU SIEGE BNI</t>
+  </si>
+  <si>
+    <t>2720303000</t>
+  </si>
+  <si>
+    <t>65534180</t>
+  </si>
+  <si>
+    <t>26/06/2026 14:35:28</t>
+  </si>
+  <si>
+    <t>65442117</t>
+  </si>
+  <si>
+    <t>25/06/2026 08:37:15</t>
+  </si>
+  <si>
+    <t>DOUANES</t>
+  </si>
+  <si>
+    <t>ABIDJAN-PORT-BOUET//VOIE INCONNUE/AEROPORT FRET DOUANES</t>
+  </si>
+  <si>
+    <t>50M</t>
+  </si>
+  <si>
+    <t>VPNLL230023</t>
+  </si>
+  <si>
+    <t>0709602414</t>
+  </si>
+  <si>
+    <t>1959236</t>
+  </si>
+  <si>
+    <t>IP Connect LL</t>
+  </si>
+  <si>
+    <t>66580530</t>
+  </si>
+  <si>
     <t>Offert</t>
   </si>
   <si>
-    <t>26/06/2026 14:30:26</t>
-  </si>
-  <si>
-    <t>65395686</t>
-  </si>
-  <si>
-    <t>24/06/2026 11:38:13</t>
-  </si>
-  <si>
-    <t>2720209800</t>
-  </si>
-  <si>
-    <t>65532878</t>
-  </si>
-  <si>
-    <t>26/06/2026 14:21:02</t>
-  </si>
-  <si>
-    <t>65400923</t>
-  </si>
-  <si>
-    <t>24/06/2026 12:37:44</t>
-  </si>
-  <si>
-    <t>BNI GESTION</t>
-  </si>
-  <si>
-    <t>SIEGE BNI PLATEAU</t>
-  </si>
-  <si>
-    <t>2720208110</t>
-  </si>
-  <si>
-    <t>T0</t>
-  </si>
-  <si>
-    <t>26/06/2026 14:59:53</t>
-  </si>
-  <si>
-    <t>65536408</t>
-  </si>
-  <si>
-    <t>65401420</t>
-  </si>
-  <si>
-    <t>24/06/2026 12:44:36</t>
-  </si>
-  <si>
-    <t>2720310777</t>
-  </si>
-  <si>
-    <t>65533279</t>
-  </si>
-  <si>
-    <t>26/06/2026 14:26:10</t>
-  </si>
-  <si>
-    <t>65402557</t>
-  </si>
-  <si>
-    <t>24/06/2026 12:58:18</t>
-  </si>
-  <si>
-    <t>2720312270</t>
-  </si>
-  <si>
-    <t>65536161</t>
-  </si>
-  <si>
-    <t>26/06/2026 14:55:41</t>
-  </si>
-  <si>
-    <t>65411444</t>
-  </si>
-  <si>
-    <t>24/06/2026 14:51:50</t>
-  </si>
-  <si>
-    <t>PLATEAU SIEGE BNI</t>
-  </si>
-  <si>
-    <t>2720303000</t>
-  </si>
-  <si>
-    <t>65534180</t>
-  </si>
-  <si>
-    <t>26/06/2026 14:35:28</t>
-  </si>
-  <si>
-    <t>50M</t>
-  </si>
-  <si>
-    <t>IP Connect LL</t>
+    <t>BBF : Prerequis Etude</t>
+  </si>
+  <si>
+    <t>15/07/2026 10:11:02</t>
   </si>
   <si>
     <t>65530820</t>
@@ -287,12 +320,12 @@
     <t>VPNLL060103</t>
   </si>
   <si>
+    <t>06/07/2026 09:41:35</t>
+  </si>
+  <si>
     <t>66021892</t>
   </si>
   <si>
-    <t>06/07/2026 09:41:35</t>
-  </si>
-  <si>
     <t>65532025</t>
   </si>
   <si>
@@ -320,9 +353,6 @@
     <t>66022272</t>
   </si>
   <si>
-    <t>BO Homologation : Saisie GAIA LSI</t>
-  </si>
-  <si>
     <t>65532924</t>
   </si>
   <si>
@@ -335,15 +365,18 @@
     <t>SYTHD120096</t>
   </si>
   <si>
+    <t>1956466</t>
+  </si>
+  <si>
     <t>LIAISON SPECIALISEE</t>
   </si>
   <si>
+    <t>66021936</t>
+  </si>
+  <si>
     <t>06/07/2026 09:42:13</t>
   </si>
   <si>
-    <t>66021936</t>
-  </si>
-  <si>
     <t>65534223</t>
   </si>
   <si>
@@ -356,6 +389,9 @@
     <t>SYTHD250263</t>
   </si>
   <si>
+    <t>1956486</t>
+  </si>
+  <si>
     <t>66023299</t>
   </si>
   <si>
@@ -374,6 +410,9 @@
     <t>VPNLL100132</t>
   </si>
   <si>
+    <t>1956456</t>
+  </si>
+  <si>
     <t>66019680</t>
   </si>
   <si>
@@ -389,6 +428,9 @@
     <t>VPNLL120082</t>
   </si>
   <si>
+    <t>1956436</t>
+  </si>
+  <si>
     <t>06/07/2026 09:03:44</t>
   </si>
   <si>
@@ -404,106 +446,118 @@
     <t>VPNLL070228</t>
   </si>
   <si>
+    <t>1956426</t>
+  </si>
+  <si>
     <t>06/07/2026 09:05:11</t>
   </si>
   <si>
     <t>66019377</t>
   </si>
   <si>
-    <t>66190079</t>
-  </si>
-  <si>
-    <t>08/07/2026 15:06:55</t>
-  </si>
-  <si>
-    <t>LOTERIE NATIONALE DE COTE D'IVOIRE</t>
-  </si>
-  <si>
-    <t>MARCORY</t>
-  </si>
-  <si>
-    <t>LONACI STUDIO</t>
-  </si>
-  <si>
-    <t>20M</t>
-  </si>
-  <si>
-    <t>SYTHD220206</t>
+    <t>66856525</t>
+  </si>
+  <si>
+    <t>20/07/2026 10:06:12</t>
+  </si>
+  <si>
+    <t>COOPERATIVE NOUVEL ESPRIT DE KETESSO</t>
+  </si>
+  <si>
+    <t>MARCORY ZONE 4 BÂT MPME</t>
+  </si>
+  <si>
+    <t>2721250972</t>
+  </si>
+  <si>
+    <t>0748541942</t>
+  </si>
+  <si>
+    <t>67534047</t>
+  </si>
+  <si>
+    <t>31/07/2026 11:59:29</t>
+  </si>
+  <si>
+    <t>67275437</t>
+  </si>
+  <si>
+    <t>27/07/2026 15:03:54</t>
+  </si>
+  <si>
+    <t>ECOBANK COTE D'IVOIRE</t>
+  </si>
+  <si>
+    <t>ABIDJAN-PLATEAU//VOIE INCONNUE/PLATEAU RUE DU COMMERCE</t>
+  </si>
+  <si>
+    <t>SYTHD200101</t>
+  </si>
+  <si>
+    <t>0708448850</t>
+  </si>
+  <si>
+    <t>1962846</t>
+  </si>
+  <si>
+    <t>10/08/2026 11:41:06</t>
+  </si>
+  <si>
+    <t>68064519</t>
+  </si>
+  <si>
+    <t>67278960</t>
+  </si>
+  <si>
+    <t>27/07/2026 15:36:16</t>
+  </si>
+  <si>
+    <t>100M</t>
+  </si>
+  <si>
+    <t>VPNLL250027</t>
+  </si>
+  <si>
+    <t>1962816</t>
+  </si>
+  <si>
+    <t>68063959</t>
+  </si>
+  <si>
+    <t>10/08/2026 11:34:18</t>
+  </si>
+  <si>
+    <t>67279938</t>
+  </si>
+  <si>
+    <t>27/07/2026 15:44:45</t>
+  </si>
+  <si>
+    <t>150MB</t>
+  </si>
+  <si>
+    <t>VPNLL150043</t>
+  </si>
+  <si>
+    <t>1962806</t>
+  </si>
+  <si>
+    <t>68064280</t>
+  </si>
+  <si>
+    <t>10/08/2026 11:37:58</t>
+  </si>
+  <si>
+    <t>debit</t>
+  </si>
+  <si>
+    <t>10M</t>
   </si>
   <si>
     <t>Backup</t>
   </si>
   <si>
-    <t>69937804</t>
-  </si>
-  <si>
-    <t>BO Homologation: Mise en service GAIA</t>
-  </si>
-  <si>
-    <t>10/09/2026 16:40:46</t>
-  </si>
-  <si>
-    <t>67275437</t>
-  </si>
-  <si>
-    <t>27/07/2026 15:03:54</t>
-  </si>
-  <si>
-    <t>ECOBANK COTE D'IVOIRE</t>
-  </si>
-  <si>
-    <t>ABIDJAN-PLATEAU//VOIE INCONNUE/PLATEAU RUE DU COMMERCE</t>
-  </si>
-  <si>
-    <t>SYTHD200101</t>
-  </si>
-  <si>
-    <t>10/08/2026 11:41:06</t>
-  </si>
-  <si>
-    <t>68064519</t>
-  </si>
-  <si>
-    <t>67278960</t>
-  </si>
-  <si>
-    <t>27/07/2026 15:36:16</t>
-  </si>
-  <si>
-    <t>100M</t>
-  </si>
-  <si>
-    <t>VPNLL250027</t>
-  </si>
-  <si>
-    <t>68063959</t>
-  </si>
-  <si>
-    <t>10/08/2026 11:34:18</t>
-  </si>
-  <si>
-    <t>67279938</t>
-  </si>
-  <si>
-    <t>27/07/2026 15:44:45</t>
-  </si>
-  <si>
-    <t>150MB</t>
-  </si>
-  <si>
-    <t>VPNLL150043</t>
-  </si>
-  <si>
-    <t>68064280</t>
-  </si>
-  <si>
-    <t>10/08/2026 11:37:58</t>
-  </si>
-  <si>
-    <t>debit</t>
-  </si>
-  <si>
-    <t>radio</t>
+    <t>40M</t>
   </si>
   <si>
     <t>69410226</t>
@@ -515,16 +569,25 @@
     <t>CORIS BANK INTERNATIONAL</t>
   </si>
   <si>
+    <t>ABIDJAN-MARCORY//VOIE INCONNUE/</t>
+  </si>
+  <si>
     <t>4M</t>
   </si>
   <si>
     <t>BUVPN150609</t>
   </si>
   <si>
-    <t>69928919</t>
-  </si>
-  <si>
-    <t>10/09/2026 15:13:44</t>
+    <t>0566473307</t>
+  </si>
+  <si>
+    <t>4123146</t>
+  </si>
+  <si>
+    <t>70567576</t>
+  </si>
+  <si>
+    <t>21/09/2026 08:53:56</t>
   </si>
   <si>
     <t>69410835</t>
@@ -536,10 +599,13 @@
     <t>BUVPN150618</t>
   </si>
   <si>
-    <t>69894721</t>
-  </si>
-  <si>
-    <t>10/09/2026 08:30:17</t>
+    <t>4123156</t>
+  </si>
+  <si>
+    <t>70441988</t>
+  </si>
+  <si>
+    <t>18/09/2026 16:36:46</t>
   </si>
   <si>
     <t>69411365</t>
@@ -548,16 +614,19 @@
     <t>01/09/2026 16:18:34</t>
   </si>
   <si>
-    <t>ADJAME</t>
+    <t>ABIDJAN-ADJAME//VOIE INCONNUE/</t>
   </si>
   <si>
     <t>BUVPN150554</t>
   </si>
   <si>
-    <t>10/09/2026 10:52:44</t>
-  </si>
-  <si>
-    <t>69905096</t>
+    <t>4123166</t>
+  </si>
+  <si>
+    <t>70439950</t>
+  </si>
+  <si>
+    <t>18/09/2026 16:18:20</t>
   </si>
   <si>
     <t>69411931</t>
@@ -569,82 +638,70 @@
     <t>BUVPN150555</t>
   </si>
   <si>
-    <t>69894507</t>
-  </si>
-  <si>
-    <t>10/09/2026 08:26:03</t>
-  </si>
-  <si>
-    <t>69591302</t>
-  </si>
-  <si>
-    <t>04/09/2026 15:42:51</t>
-  </si>
-  <si>
-    <t>KOIRA HOTEL INVESTMENT</t>
-  </si>
-  <si>
-    <t>PORT-BOUET</t>
-  </si>
-  <si>
-    <t>SYTHD150156</t>
-  </si>
-  <si>
-    <t>69894263</t>
-  </si>
-  <si>
-    <t>10/09/2026 08:21:38</t>
-  </si>
-  <si>
-    <t>69781366</t>
-  </si>
-  <si>
-    <t>08/09/2026 11:06:10</t>
-  </si>
-  <si>
-    <t>IHS COTE D'IVOIRE</t>
-  </si>
-  <si>
-    <t>MARCORY ZONE 4</t>
-  </si>
-  <si>
-    <t>SYTHD130177</t>
-  </si>
-  <si>
-    <t>69978542</t>
-  </si>
-  <si>
-    <t>11/09/2026 12:25:52</t>
+    <t>4123176</t>
+  </si>
+  <si>
+    <t>70440219</t>
+  </si>
+  <si>
+    <t>18/09/2026 16:20:28</t>
+  </si>
+  <si>
+    <t>69808884</t>
+  </si>
+  <si>
+    <t>08/09/2026 15:59:57</t>
   </si>
   <si>
     <t>AFGBANK COTE D'IVOIRE</t>
   </si>
   <si>
+    <t>KORHOGO//VOIE INCONNUE/KORHOGO</t>
+  </si>
+  <si>
     <t>5M</t>
   </si>
   <si>
-    <t>69965942</t>
-  </si>
-  <si>
-    <t>11/09/2026 10:16:25</t>
-  </si>
-  <si>
-    <t>WAVE COTE D'IVOIRE SA</t>
-  </si>
-  <si>
-    <t>BOUAKE</t>
-  </si>
-  <si>
-    <t>150M</t>
-  </si>
-  <si>
-    <t>SYTHD250167</t>
-  </si>
-  <si>
-    <t>11/09/2026 10:16:52</t>
-  </si>
-  <si>
-    <t>69965997</t>
+    <t>BUVPN220237</t>
+  </si>
+  <si>
+    <t>0707984429</t>
+  </si>
+  <si>
+    <t>4122686</t>
+  </si>
+  <si>
+    <t>70405897</t>
+  </si>
+  <si>
+    <t>18/09/2026 11:20:19</t>
+  </si>
+  <si>
+    <t>69834889</t>
+  </si>
+  <si>
+    <t>09/09/2026 08:57:40</t>
+  </si>
+  <si>
+    <t>GLOVOAPP COTE D'IVOIRE</t>
+  </si>
+  <si>
+    <t>ABIDJAN-COCODY//VOIE INCONNUE/RIVIERA MBADON</t>
+  </si>
+  <si>
+    <t>SYTHD250285</t>
+  </si>
+  <si>
+    <t>0788492751</t>
+  </si>
+  <si>
+    <t>4122636</t>
+  </si>
+  <si>
+    <t>70440697</t>
+  </si>
+  <si>
+    <t>18/09/2026 16:25:27</t>
   </si>
   <si>
     <t>69973725</t>
@@ -662,70 +719,247 @@
     <t>2722533513</t>
   </si>
   <si>
+    <t>0769589517</t>
+  </si>
+  <si>
     <t>70105593</t>
   </si>
   <si>
     <t>14/09/2026 10:28:26</t>
   </si>
   <si>
-    <t>69974913</t>
-  </si>
-  <si>
-    <t>11/09/2026 11:47:19</t>
-  </si>
-  <si>
-    <t>TRANSFERT DE LIEN SUR TRINGRELA</t>
-  </si>
-  <si>
-    <t>BUVPN240192</t>
-  </si>
-  <si>
-    <t>11/09/2026 11:47:40</t>
-  </si>
-  <si>
-    <t>69974948</t>
-  </si>
-  <si>
-    <t>69979511</t>
-  </si>
-  <si>
-    <t>11/09/2026 12:34:51</t>
-  </si>
-  <si>
-    <t>NOUVELLE BRASSERIE DE COTE D'IVOIRE</t>
+    <t>70138842</t>
+  </si>
+  <si>
+    <t>14/09/2026 16:28:53</t>
+  </si>
+  <si>
+    <t>ABIDJAN-PLATEAU//VOIE INCONNUE/RUE DES BANQUES</t>
+  </si>
+  <si>
+    <t>BUVPN150379</t>
+  </si>
+  <si>
+    <t>4123466</t>
+  </si>
+  <si>
+    <t>70567966</t>
+  </si>
+  <si>
+    <t>21/09/2026 09:00:22</t>
+  </si>
+  <si>
+    <t>70243760</t>
+  </si>
+  <si>
+    <t>16/09/2026 10:21:20</t>
+  </si>
+  <si>
+    <t>PLATEAU RUE DU COMMERCE</t>
   </si>
   <si>
     <t>256K</t>
   </si>
   <si>
-    <t>2721239560</t>
-  </si>
-  <si>
-    <t>70105360</t>
-  </si>
-  <si>
-    <t>14/09/2026 10:25:31</t>
-  </si>
-  <si>
-    <t>69998201</t>
-  </si>
-  <si>
-    <t>11/09/2026 16:07:04</t>
-  </si>
-  <si>
-    <t>STE SIFCOM</t>
-  </si>
-  <si>
-    <t>BD DE VRIODI IMMEUBLE COMAFRIQUE</t>
-  </si>
-  <si>
-    <t>SYTHD110016</t>
-  </si>
-  <si>
-    <t>69998240</t>
-  </si>
-  <si>
-    <t>11/09/2026 16:07:32</t>
+    <t>2720215000</t>
+  </si>
+  <si>
+    <t>0709054672</t>
+  </si>
+  <si>
+    <t>T0 VIRAGE</t>
+  </si>
+  <si>
+    <t>70570395</t>
+  </si>
+  <si>
+    <t>21/09/2026 09:36:28</t>
+  </si>
+  <si>
+    <t>70245071</t>
+  </si>
+  <si>
+    <t>16/09/2026 10:35:30</t>
+  </si>
+  <si>
+    <t>2720256500</t>
+  </si>
+  <si>
+    <t>70571149</t>
+  </si>
+  <si>
+    <t>21/09/2026 09:47:20</t>
+  </si>
+  <si>
+    <t>70246354</t>
+  </si>
+  <si>
+    <t>16/09/2026 10:49:25</t>
+  </si>
+  <si>
+    <t>2720319200</t>
+  </si>
+  <si>
+    <t>70569509</t>
+  </si>
+  <si>
+    <t>21/09/2026 09:24:35</t>
+  </si>
+  <si>
+    <t>70247656</t>
+  </si>
+  <si>
+    <t>16/09/2026 11:02:16</t>
+  </si>
+  <si>
+    <t>ECOBANK ASSET MANAGEMENT</t>
+  </si>
+  <si>
+    <t>2720222668</t>
+  </si>
+  <si>
+    <t>70571495</t>
+  </si>
+  <si>
+    <t>21/09/2026 09:51:42</t>
+  </si>
+  <si>
+    <t>70364528</t>
+  </si>
+  <si>
+    <t>17/09/2026 16:51:24</t>
+  </si>
+  <si>
+    <t>BATIM COTE D'IVOIRE</t>
+  </si>
+  <si>
+    <t>COCODY RIVIERA BONOUMIN</t>
+  </si>
+  <si>
+    <t>2722520150</t>
+  </si>
+  <si>
+    <t>0777143494</t>
+  </si>
+  <si>
+    <t>70570076</t>
+  </si>
+  <si>
+    <t>21/09/2026 09:33:19</t>
+  </si>
+  <si>
+    <t>70409532</t>
+  </si>
+  <si>
+    <t>18/09/2026 11:58:21</t>
+  </si>
+  <si>
+    <t>PLATEAU RUE DES BANQUES</t>
+  </si>
+  <si>
+    <t>BUVPN260031</t>
+  </si>
+  <si>
+    <t>18/09/2026 11:58:33</t>
+  </si>
+  <si>
+    <t>70409576</t>
+  </si>
+  <si>
+    <t>70410500</t>
+  </si>
+  <si>
+    <t>18/09/2026 12:06:46</t>
+  </si>
+  <si>
+    <t>PLATEAU RUE  DES BANQUES</t>
+  </si>
+  <si>
+    <t>15M</t>
+  </si>
+  <si>
+    <t>BUVPN260024</t>
+  </si>
+  <si>
+    <t>70410525</t>
+  </si>
+  <si>
+    <t>18/09/2026 12:06:52</t>
+  </si>
+  <si>
+    <t>70411823</t>
+  </si>
+  <si>
+    <t>18/09/2026 12:21:46</t>
+  </si>
+  <si>
+    <t>SUNU ASSURANCES IARD</t>
+  </si>
+  <si>
+    <t>SYTHD250103</t>
+  </si>
+  <si>
+    <t>0789301530</t>
+  </si>
+  <si>
+    <t>70411843</t>
+  </si>
+  <si>
+    <t>18/09/2026 12:21:54</t>
+  </si>
+  <si>
+    <t>70415619</t>
+  </si>
+  <si>
+    <t>18/09/2026 13:10:14</t>
+  </si>
+  <si>
+    <t>SUNU Assurances Vie Côte d'Ivoire</t>
+  </si>
+  <si>
+    <t>PLATEAU IMMEUBLE VERDIER 9 AVENUE HOUDAILLE</t>
+  </si>
+  <si>
+    <t>SYTHD250155</t>
+  </si>
+  <si>
+    <t>0759419145</t>
+  </si>
+  <si>
+    <t>70415636</t>
+  </si>
+  <si>
+    <t>18/09/2026 13:10:21</t>
+  </si>
+  <si>
+    <t>70428204</t>
+  </si>
+  <si>
+    <t>18/09/2026 15:15:06</t>
+  </si>
+  <si>
+    <t>GIABA CENTRE D'INFORMATION D'ABIDJAN</t>
+  </si>
+  <si>
+    <t>COCODY ANGRE</t>
+  </si>
+  <si>
+    <t>128K</t>
+  </si>
+  <si>
+    <t>2722514710</t>
+  </si>
+  <si>
+    <t>0758177749</t>
+  </si>
+  <si>
+    <t>70428281</t>
+  </si>
+  <si>
+    <t>18/09/2026 15:15:42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BBF : Prerequis Etude : </t>
   </si>
 </sst>
 </file>
@@ -1102,31 +1336,33 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S30"/>
+  <dimension ref="A1:U38"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" style="1" customWidth="1"/>
     <col min="3" max="3" width="29.6640625" style="1" customWidth="1"/>
     <col min="4" max="4" width="49.1640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="45.33203125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="44.08203125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="49.5" style="1" customWidth="1"/>
-    <col min="8" max="8" width="59.5" style="1" customWidth="1"/>
-    <col min="9" max="9" width="44.83203125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="38.33203125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="29.1640625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="25.83203125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="69.83203125" style="1" customWidth="1"/>
-    <col min="14" max="14" width="35.6640625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="33" style="1" customWidth="1"/>
-    <col min="16" max="16" width="34.9140625" style="1" customWidth="1"/>
-    <col min="17" max="17" width="37.9140625" customWidth="1"/>
-    <col min="18" max="18" width="39.9140625" customWidth="1"/>
-    <col min="19" max="19" width="48.58203125" customWidth="1"/>
+    <col min="5" max="5" width="44.08203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="49.5" style="1" customWidth="1"/>
+    <col min="7" max="7" width="59.5" style="1" customWidth="1"/>
+    <col min="8" max="8" width="44.83203125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="38.33203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="29.1640625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="25.83203125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="69.83203125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="35.6640625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="33" style="1" customWidth="1"/>
+    <col min="15" max="15" width="34.9140625" style="1" customWidth="1"/>
+    <col min="16" max="16" width="35" style="1" customWidth="1"/>
+    <col min="17" max="17" width="34.83203125" customWidth="1"/>
+    <col min="18" max="18" width="50.5" customWidth="1"/>
+    <col min="19" max="19" width="37.9140625" customWidth="1"/>
+    <col min="20" max="20" width="39.9140625" customWidth="1"/>
+    <col min="21" max="21" width="48.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1170,22 +1406,28 @@
         <v>16</v>
       </c>
       <c r="O1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="P1" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="S1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="S1" s="2" t="s">
-        <v>18</v>
+      <c r="U1" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>30</v>
       </c>
@@ -1199,37 +1441,37 @@
         <v>33</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="F2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H2" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="I2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J2" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="K2" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="L2" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="M2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N2" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="O2" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="P2" t="s">
         <v>37</v>
@@ -1238,18 +1480,24 @@
         <v>38</v>
       </c>
       <c r="R2" t="s">
+        <v>21</v>
+      </c>
+      <c r="S2" t="s">
         <v>39</v>
       </c>
-      <c r="S2" t="s">
+      <c r="T2" t="s">
+        <v>40</v>
+      </c>
+      <c r="U2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C3" t="s">
         <v>32</v>
@@ -1258,52 +1506,58 @@
         <v>33</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="F3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H3" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="I3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J3" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="K3" t="s">
+        <v>29</v>
+      </c>
+      <c r="L3" t="s">
+        <v>42</v>
+      </c>
+      <c r="M3" t="s">
+        <v>48</v>
+      </c>
+      <c r="N3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O3" t="s">
         <v>46</v>
       </c>
-      <c r="L3" t="s">
-        <v>47</v>
-      </c>
-      <c r="M3" t="s">
-        <v>41</v>
-      </c>
-      <c r="N3" t="s">
-        <v>48</v>
-      </c>
-      <c r="O3" t="s">
-        <v>19</v>
-      </c>
       <c r="P3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q3" t="s">
         <v>38</v>
       </c>
       <c r="R3" t="s">
+        <v>21</v>
+      </c>
+      <c r="S3" t="s">
         <v>39</v>
       </c>
-      <c r="S3" t="s">
+      <c r="T3" t="s">
+        <v>40</v>
+      </c>
+      <c r="U3" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>49</v>
       </c>
@@ -1317,37 +1571,37 @@
         <v>33</v>
       </c>
       <c r="E4" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="F4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H4" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="I4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J4" t="s">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="K4" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="L4" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="M4" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="N4" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="O4" t="s">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="P4" t="s">
         <v>51</v>
@@ -1356,13 +1610,19 @@
         <v>38</v>
       </c>
       <c r="R4" t="s">
+        <v>21</v>
+      </c>
+      <c r="S4" t="s">
         <v>39</v>
       </c>
-      <c r="S4" t="s">
+      <c r="T4" t="s">
+        <v>40</v>
+      </c>
+      <c r="U4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>54</v>
       </c>
@@ -1376,52 +1636,58 @@
         <v>33</v>
       </c>
       <c r="E5" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="F5" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="G5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H5" t="s">
-        <v>57</v>
+        <v>21</v>
       </c>
       <c r="I5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J5" t="s">
-        <v>19</v>
+        <v>61</v>
       </c>
       <c r="K5" t="s">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="L5" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="M5" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="N5" t="s">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="O5" t="s">
-        <v>19</v>
+        <v>58</v>
       </c>
       <c r="P5" t="s">
         <v>58</v>
       </c>
       <c r="Q5" t="s">
+        <v>38</v>
+      </c>
+      <c r="R5" t="s">
+        <v>21</v>
+      </c>
+      <c r="S5" t="s">
         <v>59</v>
       </c>
-      <c r="R5" t="s">
-        <v>39</v>
-      </c>
-      <c r="S5" t="s">
+      <c r="T5" t="s">
+        <v>40</v>
+      </c>
+      <c r="U5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>62</v>
       </c>
@@ -1435,52 +1701,58 @@
         <v>33</v>
       </c>
       <c r="E6" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="F6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G6" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="H6" t="s">
-        <v>57</v>
+        <v>21</v>
       </c>
       <c r="I6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J6" t="s">
-        <v>19</v>
+        <v>65</v>
       </c>
       <c r="K6" t="s">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="L6" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="M6" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="N6" t="s">
-        <v>66</v>
+        <v>21</v>
       </c>
       <c r="O6" t="s">
-        <v>19</v>
+        <v>64</v>
       </c>
       <c r="P6" t="s">
         <v>64</v>
       </c>
       <c r="Q6" t="s">
+        <v>38</v>
+      </c>
+      <c r="R6" t="s">
+        <v>21</v>
+      </c>
+      <c r="S6" t="s">
         <v>59</v>
       </c>
-      <c r="R6" t="s">
-        <v>39</v>
-      </c>
-      <c r="S6" t="s">
+      <c r="T6" t="s">
+        <v>40</v>
+      </c>
+      <c r="U6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>67</v>
       </c>
@@ -1494,52 +1766,58 @@
         <v>33</v>
       </c>
       <c r="E7" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="F7" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="G7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H7" t="s">
-        <v>57</v>
+        <v>21</v>
       </c>
       <c r="I7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J7" t="s">
-        <v>19</v>
+        <v>70</v>
       </c>
       <c r="K7" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="L7" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="M7" t="s">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="N7" t="s">
-        <v>71</v>
+        <v>21</v>
       </c>
       <c r="O7" t="s">
-        <v>19</v>
+        <v>69</v>
       </c>
       <c r="P7" t="s">
         <v>69</v>
       </c>
       <c r="Q7" t="s">
+        <v>38</v>
+      </c>
+      <c r="R7" t="s">
+        <v>21</v>
+      </c>
+      <c r="S7" t="s">
         <v>59</v>
       </c>
-      <c r="R7" t="s">
-        <v>39</v>
-      </c>
-      <c r="S7" t="s">
+      <c r="T7" t="s">
+        <v>40</v>
+      </c>
+      <c r="U7" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>72</v>
       </c>
@@ -1553,37 +1831,37 @@
         <v>33</v>
       </c>
       <c r="E8" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="F8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G8" t="s">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="H8" t="s">
-        <v>74</v>
+        <v>21</v>
       </c>
       <c r="I8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J8" t="s">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="K8" t="s">
-        <v>76</v>
+        <v>29</v>
       </c>
       <c r="L8" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="M8" t="s">
-        <v>41</v>
+        <v>77</v>
       </c>
       <c r="N8" t="s">
-        <v>77</v>
+        <v>21</v>
       </c>
       <c r="O8" t="s">
-        <v>19</v>
+        <v>75</v>
       </c>
       <c r="P8" t="s">
         <v>75</v>
@@ -1592,18 +1870,24 @@
         <v>38</v>
       </c>
       <c r="R8" t="s">
+        <v>21</v>
+      </c>
+      <c r="S8" t="s">
         <v>39</v>
       </c>
-      <c r="S8" t="s">
+      <c r="T8" t="s">
+        <v>40</v>
+      </c>
+      <c r="U8" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B9" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C9" t="s">
         <v>32</v>
@@ -1612,57 +1896,63 @@
         <v>22</v>
       </c>
       <c r="E9" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F9" t="s">
-        <v>23</v>
+        <v>80</v>
       </c>
       <c r="G9" t="s">
-        <v>35</v>
+        <v>81</v>
       </c>
       <c r="H9" t="s">
         <v>82</v>
       </c>
       <c r="I9" t="s">
+        <v>21</v>
+      </c>
+      <c r="J9" t="s">
+        <v>87</v>
+      </c>
+      <c r="K9" t="s">
+        <v>88</v>
+      </c>
+      <c r="L9" t="s">
+        <v>309</v>
+      </c>
+      <c r="M9" t="s">
+        <v>90</v>
+      </c>
+      <c r="N9" t="s">
+        <v>21</v>
+      </c>
+      <c r="O9" t="s">
         <v>83</v>
       </c>
-      <c r="J9" t="s">
-        <v>19</v>
-      </c>
-      <c r="K9" t="s">
+      <c r="P9" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>84</v>
+      </c>
+      <c r="R9" t="s">
         <v>85</v>
       </c>
-      <c r="L9" t="s">
-        <v>47</v>
-      </c>
-      <c r="M9" t="s">
-        <v>41</v>
-      </c>
-      <c r="N9" t="s">
+      <c r="S9" t="s">
         <v>86</v>
       </c>
-      <c r="O9" t="s">
-        <v>19</v>
-      </c>
-      <c r="P9" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>24</v>
-      </c>
-      <c r="R9" t="s">
+      <c r="T9" t="s">
         <v>25</v>
       </c>
-      <c r="S9" t="s">
+      <c r="U9" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B10" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C10" t="s">
         <v>32</v>
@@ -1671,57 +1961,63 @@
         <v>22</v>
       </c>
       <c r="E10" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F10" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="G10" t="s">
-        <v>35</v>
+        <v>93</v>
       </c>
       <c r="H10" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="I10" t="s">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="J10" t="s">
-        <v>19</v>
+        <v>97</v>
       </c>
       <c r="K10" t="s">
+        <v>29</v>
+      </c>
+      <c r="L10" t="s">
+        <v>42</v>
+      </c>
+      <c r="M10" t="s">
+        <v>96</v>
+      </c>
+      <c r="N10" t="s">
+        <v>21</v>
+      </c>
+      <c r="O10" t="s">
         <v>95</v>
       </c>
-      <c r="L10" t="s">
-        <v>47</v>
-      </c>
-      <c r="M10" t="s">
-        <v>41</v>
-      </c>
-      <c r="N10" t="s">
-        <v>94</v>
-      </c>
-      <c r="O10" t="s">
-        <v>19</v>
-      </c>
       <c r="P10" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="Q10" t="s">
-        <v>92</v>
+        <v>38</v>
       </c>
       <c r="R10" t="s">
-        <v>93</v>
+        <v>21</v>
       </c>
       <c r="S10" t="s">
+        <v>24</v>
+      </c>
+      <c r="T10" t="s">
+        <v>25</v>
+      </c>
+      <c r="U10" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C11" t="s">
         <v>32</v>
@@ -1730,57 +2026,63 @@
         <v>22</v>
       </c>
       <c r="E11" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F11" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="G11" t="s">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="H11" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I11" t="s">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="J11" t="s">
-        <v>19</v>
+        <v>106</v>
       </c>
       <c r="K11" t="s">
+        <v>29</v>
+      </c>
+      <c r="L11" t="s">
+        <v>42</v>
+      </c>
+      <c r="M11" t="s">
+        <v>105</v>
+      </c>
+      <c r="N11" t="s">
+        <v>21</v>
+      </c>
+      <c r="O11" t="s">
+        <v>102</v>
+      </c>
+      <c r="P11" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>38</v>
+      </c>
+      <c r="R11" t="s">
+        <v>21</v>
+      </c>
+      <c r="S11" t="s">
         <v>103</v>
       </c>
-      <c r="L11" t="s">
-        <v>47</v>
-      </c>
-      <c r="M11" t="s">
-        <v>41</v>
-      </c>
-      <c r="N11" t="s">
-        <v>102</v>
-      </c>
-      <c r="O11" t="s">
-        <v>19</v>
-      </c>
-      <c r="P11" t="s">
-        <v>100</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>101</v>
-      </c>
-      <c r="R11" t="s">
-        <v>93</v>
-      </c>
-      <c r="S11" t="s">
+      <c r="T11" t="s">
+        <v>104</v>
+      </c>
+      <c r="U11" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B12" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C12" t="s">
         <v>32</v>
@@ -1789,57 +2091,63 @@
         <v>22</v>
       </c>
       <c r="E12" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F12" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="G12" t="s">
-        <v>35</v>
+        <v>109</v>
       </c>
       <c r="H12" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I12" t="s">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="J12" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
       <c r="K12" t="s">
-        <v>108</v>
+        <v>29</v>
       </c>
       <c r="L12" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="M12" t="s">
-        <v>41</v>
+        <v>114</v>
       </c>
       <c r="N12" t="s">
-        <v>109</v>
+        <v>21</v>
       </c>
       <c r="O12" t="s">
-        <v>19</v>
+        <v>110</v>
       </c>
       <c r="P12" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="Q12" t="s">
-        <v>101</v>
+        <v>38</v>
       </c>
       <c r="R12" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="S12" t="s">
+        <v>112</v>
+      </c>
+      <c r="T12" t="s">
+        <v>104</v>
+      </c>
+      <c r="U12" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B13" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C13" t="s">
         <v>32</v>
@@ -1848,57 +2156,63 @@
         <v>22</v>
       </c>
       <c r="E13" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F13" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="G13" t="s">
-        <v>35</v>
+        <v>109</v>
       </c>
       <c r="H13" t="s">
+        <v>117</v>
+      </c>
+      <c r="I13" t="s">
+        <v>21</v>
+      </c>
+      <c r="J13" t="s">
+        <v>120</v>
+      </c>
+      <c r="K13" t="s">
+        <v>29</v>
+      </c>
+      <c r="L13" t="s">
+        <v>42</v>
+      </c>
+      <c r="M13" t="s">
+        <v>121</v>
+      </c>
+      <c r="N13" t="s">
+        <v>21</v>
+      </c>
+      <c r="O13" t="s">
+        <v>118</v>
+      </c>
+      <c r="P13" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>38</v>
+      </c>
+      <c r="R13" t="s">
+        <v>119</v>
+      </c>
+      <c r="S13" t="s">
         <v>112</v>
       </c>
-      <c r="I13" t="s">
-        <v>83</v>
-      </c>
-      <c r="J13" t="s">
-        <v>19</v>
-      </c>
-      <c r="K13" t="s">
-        <v>114</v>
-      </c>
-      <c r="L13" t="s">
-        <v>47</v>
-      </c>
-      <c r="M13" t="s">
-        <v>41</v>
-      </c>
-      <c r="N13" t="s">
-        <v>115</v>
-      </c>
-      <c r="O13" t="s">
-        <v>19</v>
-      </c>
-      <c r="P13" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>79</v>
-      </c>
-      <c r="R13" t="s">
-        <v>25</v>
-      </c>
-      <c r="S13" t="s">
+      <c r="T13" t="s">
+        <v>104</v>
+      </c>
+      <c r="U13" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B14" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="C14" t="s">
         <v>32</v>
@@ -1907,57 +2221,63 @@
         <v>22</v>
       </c>
       <c r="E14" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F14" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="G14" t="s">
-        <v>35</v>
+        <v>124</v>
       </c>
       <c r="H14" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="I14" t="s">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="J14" t="s">
-        <v>19</v>
+        <v>127</v>
       </c>
       <c r="K14" t="s">
-        <v>120</v>
+        <v>29</v>
       </c>
       <c r="L14" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="M14" t="s">
-        <v>41</v>
+        <v>128</v>
       </c>
       <c r="N14" t="s">
-        <v>119</v>
+        <v>21</v>
       </c>
       <c r="O14" t="s">
-        <v>19</v>
+        <v>125</v>
       </c>
       <c r="P14" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="Q14" t="s">
-        <v>79</v>
+        <v>38</v>
       </c>
       <c r="R14" t="s">
+        <v>126</v>
+      </c>
+      <c r="S14" t="s">
+        <v>86</v>
+      </c>
+      <c r="T14" t="s">
         <v>25</v>
       </c>
-      <c r="S14" t="s">
+      <c r="U14" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="B15" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="C15" t="s">
         <v>32</v>
@@ -1966,175 +2286,193 @@
         <v>22</v>
       </c>
       <c r="E15" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F15" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="G15" t="s">
-        <v>35</v>
+        <v>124</v>
       </c>
       <c r="H15" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="I15" t="s">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="J15" t="s">
-        <v>19</v>
+        <v>134</v>
       </c>
       <c r="K15" t="s">
-        <v>125</v>
+        <v>29</v>
       </c>
       <c r="L15" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="M15" t="s">
-        <v>41</v>
+        <v>133</v>
       </c>
       <c r="N15" t="s">
-        <v>124</v>
+        <v>21</v>
       </c>
       <c r="O15" t="s">
-        <v>19</v>
+        <v>131</v>
       </c>
       <c r="P15" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="Q15" t="s">
-        <v>79</v>
+        <v>38</v>
       </c>
       <c r="R15" t="s">
+        <v>132</v>
+      </c>
+      <c r="S15" t="s">
+        <v>86</v>
+      </c>
+      <c r="T15" t="s">
         <v>25</v>
       </c>
-      <c r="S15" t="s">
+      <c r="U15" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="B16" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="C16" t="s">
         <v>32</v>
       </c>
       <c r="D16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F16" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="G16" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="H16" t="s">
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="I16" t="s">
-        <v>131</v>
+        <v>21</v>
       </c>
       <c r="J16" t="s">
-        <v>19</v>
+        <v>140</v>
       </c>
       <c r="K16" t="s">
-        <v>134</v>
+        <v>29</v>
       </c>
       <c r="L16" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="M16" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="N16" t="s">
-        <v>136</v>
+        <v>21</v>
       </c>
       <c r="O16" t="s">
-        <v>19</v>
+        <v>137</v>
       </c>
       <c r="P16" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="Q16" t="s">
-        <v>92</v>
+        <v>38</v>
       </c>
       <c r="R16" t="s">
-        <v>93</v>
+        <v>138</v>
       </c>
       <c r="S16" t="s">
-        <v>133</v>
+        <v>86</v>
+      </c>
+      <c r="T16" t="s">
+        <v>25</v>
+      </c>
+      <c r="U16" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B17" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C17" t="s">
         <v>32</v>
       </c>
       <c r="D17" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="E17" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="F17" t="s">
-        <v>23</v>
+        <v>143</v>
       </c>
       <c r="G17" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="H17" t="s">
-        <v>140</v>
+        <v>21</v>
       </c>
       <c r="I17" t="s">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="J17" t="s">
-        <v>19</v>
+        <v>147</v>
       </c>
       <c r="K17" t="s">
-        <v>143</v>
+        <v>88</v>
       </c>
       <c r="L17" t="s">
-        <v>47</v>
+        <v>89</v>
       </c>
       <c r="M17" t="s">
-        <v>41</v>
+        <v>148</v>
       </c>
       <c r="N17" t="s">
-        <v>142</v>
+        <v>21</v>
       </c>
       <c r="O17" t="s">
-        <v>19</v>
+        <v>145</v>
       </c>
       <c r="P17" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="Q17" t="s">
-        <v>101</v>
+        <v>146</v>
       </c>
       <c r="R17" t="s">
-        <v>93</v>
+        <v>21</v>
       </c>
       <c r="S17" t="s">
+        <v>59</v>
+      </c>
+      <c r="T17" t="s">
+        <v>40</v>
+      </c>
+      <c r="U17" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="B18" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="C18" t="s">
         <v>32</v>
@@ -2143,57 +2481,63 @@
         <v>22</v>
       </c>
       <c r="E18" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F18" t="s">
-        <v>23</v>
+        <v>151</v>
       </c>
       <c r="G18" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="H18" t="s">
-        <v>140</v>
+        <v>117</v>
       </c>
       <c r="I18" t="s">
-        <v>146</v>
+        <v>21</v>
       </c>
       <c r="J18" t="s">
-        <v>19</v>
+        <v>157</v>
       </c>
       <c r="K18" t="s">
-        <v>148</v>
+        <v>29</v>
       </c>
       <c r="L18" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="M18" t="s">
-        <v>41</v>
+        <v>156</v>
       </c>
       <c r="N18" t="s">
-        <v>149</v>
+        <v>21</v>
       </c>
       <c r="O18" t="s">
-        <v>19</v>
+        <v>153</v>
       </c>
       <c r="P18" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="Q18" t="s">
-        <v>79</v>
+        <v>154</v>
       </c>
       <c r="R18" t="s">
-        <v>25</v>
+        <v>155</v>
       </c>
       <c r="S18" t="s">
+        <v>112</v>
+      </c>
+      <c r="T18" t="s">
+        <v>104</v>
+      </c>
+      <c r="U18" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="B19" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="C19" t="s">
         <v>32</v>
@@ -2202,57 +2546,63 @@
         <v>22</v>
       </c>
       <c r="E19" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F19" t="s">
-        <v>23</v>
+        <v>151</v>
       </c>
       <c r="G19" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="H19" t="s">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="I19" t="s">
-        <v>152</v>
+        <v>21</v>
       </c>
       <c r="J19" t="s">
-        <v>19</v>
+        <v>163</v>
       </c>
       <c r="K19" t="s">
+        <v>29</v>
+      </c>
+      <c r="L19" t="s">
+        <v>42</v>
+      </c>
+      <c r="M19" t="s">
+        <v>164</v>
+      </c>
+      <c r="N19" t="s">
+        <v>21</v>
+      </c>
+      <c r="O19" t="s">
+        <v>161</v>
+      </c>
+      <c r="P19" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q19" t="s">
         <v>154</v>
       </c>
-      <c r="L19" t="s">
-        <v>29</v>
-      </c>
-      <c r="M19" t="s">
-        <v>41</v>
-      </c>
-      <c r="N19" t="s">
-        <v>155</v>
-      </c>
-      <c r="O19" t="s">
-        <v>19</v>
-      </c>
-      <c r="P19" t="s">
-        <v>153</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>79</v>
-      </c>
       <c r="R19" t="s">
+        <v>162</v>
+      </c>
+      <c r="S19" t="s">
+        <v>86</v>
+      </c>
+      <c r="T19" t="s">
         <v>25</v>
       </c>
-      <c r="S19" t="s">
+      <c r="U19" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="B20" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="C20" t="s">
         <v>32</v>
@@ -2261,57 +2611,63 @@
         <v>22</v>
       </c>
       <c r="E20" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F20" t="s">
-        <v>23</v>
+        <v>151</v>
       </c>
       <c r="G20" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="H20" t="s">
-        <v>129</v>
+        <v>167</v>
       </c>
       <c r="I20" t="s">
-        <v>161</v>
+        <v>21</v>
       </c>
       <c r="J20" t="s">
-        <v>19</v>
+        <v>170</v>
       </c>
       <c r="K20" t="s">
-        <v>163</v>
+        <v>29</v>
       </c>
       <c r="L20" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="M20" t="s">
-        <v>27</v>
+        <v>171</v>
       </c>
       <c r="N20" t="s">
-        <v>164</v>
+        <v>21</v>
       </c>
       <c r="O20" t="s">
-        <v>19</v>
+        <v>168</v>
       </c>
       <c r="P20" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="Q20" t="s">
-        <v>24</v>
+        <v>154</v>
       </c>
       <c r="R20" t="s">
+        <v>169</v>
+      </c>
+      <c r="S20" t="s">
+        <v>86</v>
+      </c>
+      <c r="T20" t="s">
         <v>25</v>
       </c>
-      <c r="S20" t="s">
+      <c r="U20" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="B21" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="C21" t="s">
         <v>32</v>
@@ -2320,57 +2676,63 @@
         <v>22</v>
       </c>
       <c r="E21" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F21" t="s">
-        <v>23</v>
+        <v>178</v>
       </c>
       <c r="G21" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="H21" t="s">
-        <v>129</v>
+        <v>180</v>
       </c>
       <c r="I21" t="s">
-        <v>161</v>
+        <v>21</v>
       </c>
       <c r="J21" t="s">
-        <v>19</v>
+        <v>184</v>
       </c>
       <c r="K21" t="s">
-        <v>168</v>
+        <v>88</v>
       </c>
       <c r="L21" t="s">
-        <v>29</v>
+        <v>89</v>
       </c>
       <c r="M21" t="s">
-        <v>28</v>
+        <v>185</v>
       </c>
       <c r="N21" t="s">
-        <v>169</v>
+        <v>21</v>
       </c>
       <c r="O21" t="s">
-        <v>19</v>
+        <v>181</v>
       </c>
       <c r="P21" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="Q21" t="s">
-        <v>24</v>
+        <v>182</v>
       </c>
       <c r="R21" t="s">
+        <v>183</v>
+      </c>
+      <c r="S21" t="s">
+        <v>86</v>
+      </c>
+      <c r="T21" t="s">
         <v>25</v>
       </c>
-      <c r="S21" t="s">
-        <v>133</v>
+      <c r="U21" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="B22" t="s">
-        <v>171</v>
+        <v>187</v>
       </c>
       <c r="C22" t="s">
         <v>32</v>
@@ -2379,57 +2741,63 @@
         <v>22</v>
       </c>
       <c r="E22" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F22" t="s">
-        <v>23</v>
+        <v>178</v>
       </c>
       <c r="G22" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="H22" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="I22" t="s">
-        <v>161</v>
+        <v>21</v>
       </c>
       <c r="J22" t="s">
-        <v>19</v>
+        <v>190</v>
       </c>
       <c r="K22" t="s">
-        <v>175</v>
+        <v>88</v>
       </c>
       <c r="L22" t="s">
-        <v>47</v>
+        <v>89</v>
       </c>
       <c r="M22" t="s">
-        <v>27</v>
+        <v>191</v>
       </c>
       <c r="N22" t="s">
+        <v>21</v>
+      </c>
+      <c r="O22" t="s">
+        <v>188</v>
+      </c>
+      <c r="P22" t="s">
+        <v>188</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>182</v>
+      </c>
+      <c r="R22" t="s">
+        <v>189</v>
+      </c>
+      <c r="S22" t="s">
+        <v>86</v>
+      </c>
+      <c r="T22" t="s">
+        <v>25</v>
+      </c>
+      <c r="U22" t="s">
         <v>174</v>
       </c>
-      <c r="O22" t="s">
-        <v>19</v>
-      </c>
-      <c r="P22" t="s">
-        <v>173</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>24</v>
-      </c>
-      <c r="R22" t="s">
-        <v>25</v>
-      </c>
-      <c r="S22" t="s">
-        <v>26</v>
-      </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>176</v>
+        <v>192</v>
       </c>
       <c r="B23" t="s">
-        <v>177</v>
+        <v>193</v>
       </c>
       <c r="C23" t="s">
         <v>32</v>
@@ -2438,234 +2806,258 @@
         <v>22</v>
       </c>
       <c r="E23" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F23" t="s">
-        <v>23</v>
+        <v>178</v>
       </c>
       <c r="G23" t="s">
-        <v>160</v>
+        <v>194</v>
       </c>
       <c r="H23" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="I23" t="s">
-        <v>161</v>
+        <v>21</v>
       </c>
       <c r="J23" t="s">
-        <v>19</v>
+        <v>197</v>
       </c>
       <c r="K23" t="s">
-        <v>179</v>
+        <v>88</v>
       </c>
       <c r="L23" t="s">
-        <v>29</v>
+        <v>89</v>
       </c>
       <c r="M23" t="s">
-        <v>28</v>
+        <v>198</v>
       </c>
       <c r="N23" t="s">
-        <v>180</v>
+        <v>21</v>
       </c>
       <c r="O23" t="s">
-        <v>19</v>
+        <v>195</v>
       </c>
       <c r="P23" t="s">
-        <v>178</v>
+        <v>195</v>
       </c>
       <c r="Q23" t="s">
-        <v>24</v>
+        <v>182</v>
       </c>
       <c r="R23" t="s">
+        <v>196</v>
+      </c>
+      <c r="S23" t="s">
+        <v>86</v>
+      </c>
+      <c r="T23" t="s">
         <v>25</v>
       </c>
-      <c r="S23" t="s">
-        <v>133</v>
+      <c r="U23" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>181</v>
+        <v>199</v>
       </c>
       <c r="B24" t="s">
-        <v>182</v>
+        <v>200</v>
       </c>
       <c r="C24" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="D24" t="s">
         <v>22</v>
       </c>
       <c r="E24" t="s">
-        <v>157</v>
+        <v>23</v>
       </c>
       <c r="F24" t="s">
-        <v>23</v>
+        <v>178</v>
       </c>
       <c r="G24" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="H24" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="I24" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J24" t="s">
-        <v>19</v>
+        <v>203</v>
       </c>
       <c r="K24" t="s">
-        <v>186</v>
+        <v>88</v>
       </c>
       <c r="L24" t="s">
-        <v>29</v>
+        <v>89</v>
       </c>
       <c r="M24" t="s">
-        <v>96</v>
+        <v>204</v>
       </c>
       <c r="N24" t="s">
-        <v>187</v>
+        <v>21</v>
       </c>
       <c r="O24" t="s">
-        <v>19</v>
+        <v>201</v>
       </c>
       <c r="P24" t="s">
-        <v>185</v>
+        <v>201</v>
       </c>
       <c r="Q24" t="s">
-        <v>92</v>
+        <v>182</v>
       </c>
       <c r="R24" t="s">
-        <v>93</v>
+        <v>202</v>
       </c>
       <c r="S24" t="s">
-        <v>26</v>
+        <v>86</v>
+      </c>
+      <c r="T24" t="s">
+        <v>25</v>
+      </c>
+      <c r="U24" t="s">
+        <v>174</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>188</v>
+        <v>205</v>
       </c>
       <c r="B25" t="s">
-        <v>189</v>
+        <v>206</v>
       </c>
       <c r="C25" t="s">
-        <v>156</v>
+        <v>32</v>
       </c>
       <c r="D25" t="s">
         <v>22</v>
       </c>
       <c r="E25" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F25" t="s">
-        <v>23</v>
+        <v>207</v>
       </c>
       <c r="G25" t="s">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="H25" t="s">
-        <v>191</v>
+        <v>209</v>
       </c>
       <c r="I25" t="s">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="J25" t="s">
-        <v>78</v>
+        <v>213</v>
       </c>
       <c r="K25" t="s">
-        <v>193</v>
+        <v>88</v>
       </c>
       <c r="L25" t="s">
-        <v>29</v>
+        <v>89</v>
       </c>
       <c r="M25" t="s">
-        <v>135</v>
+        <v>214</v>
       </c>
       <c r="N25" t="s">
-        <v>194</v>
+        <v>21</v>
       </c>
       <c r="O25" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="P25" t="s">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="Q25" t="s">
-        <v>92</v>
+        <v>211</v>
       </c>
       <c r="R25" t="s">
-        <v>93</v>
+        <v>212</v>
       </c>
       <c r="S25" t="s">
+        <v>86</v>
+      </c>
+      <c r="T25" t="s">
+        <v>25</v>
+      </c>
+      <c r="U25" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>197</v>
+        <v>215</v>
       </c>
       <c r="B26" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="C26" t="s">
-        <v>156</v>
+        <v>32</v>
       </c>
       <c r="D26" t="s">
         <v>22</v>
       </c>
       <c r="E26" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F26" t="s">
-        <v>23</v>
+        <v>217</v>
       </c>
       <c r="G26" t="s">
-        <v>199</v>
+        <v>218</v>
       </c>
       <c r="H26" t="s">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="I26" t="s">
-        <v>201</v>
+        <v>21</v>
       </c>
       <c r="J26" t="s">
-        <v>78</v>
+        <v>222</v>
       </c>
       <c r="K26" t="s">
-        <v>204</v>
+        <v>88</v>
       </c>
       <c r="L26" t="s">
-        <v>47</v>
+        <v>89</v>
       </c>
       <c r="M26" t="s">
-        <v>27</v>
+        <v>223</v>
       </c>
       <c r="N26" t="s">
-        <v>203</v>
+        <v>21</v>
       </c>
       <c r="O26" t="s">
-        <v>19</v>
+        <v>219</v>
       </c>
       <c r="P26" t="s">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="Q26" t="s">
-        <v>92</v>
+        <v>220</v>
       </c>
       <c r="R26" t="s">
-        <v>93</v>
+        <v>221</v>
       </c>
       <c r="S26" t="s">
+        <v>112</v>
+      </c>
+      <c r="T26" t="s">
+        <v>104</v>
+      </c>
+      <c r="U26" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>205</v>
+        <v>224</v>
       </c>
       <c r="B27" t="s">
-        <v>206</v>
+        <v>225</v>
       </c>
       <c r="C27" t="s">
         <v>32</v>
@@ -2674,57 +3066,63 @@
         <v>33</v>
       </c>
       <c r="E27" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="F27" t="s">
-        <v>34</v>
+        <v>226</v>
       </c>
       <c r="G27" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="H27" t="s">
-        <v>208</v>
+        <v>21</v>
       </c>
       <c r="I27" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J27" t="s">
-        <v>19</v>
+        <v>230</v>
       </c>
       <c r="K27" t="s">
-        <v>210</v>
+        <v>88</v>
       </c>
       <c r="L27" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="M27" t="s">
-        <v>28</v>
+        <v>231</v>
       </c>
       <c r="N27" t="s">
-        <v>211</v>
+        <v>21</v>
       </c>
       <c r="O27" t="s">
-        <v>19</v>
+        <v>228</v>
       </c>
       <c r="P27" t="s">
-        <v>209</v>
+        <v>228</v>
       </c>
       <c r="Q27" t="s">
+        <v>229</v>
+      </c>
+      <c r="R27" t="s">
+        <v>21</v>
+      </c>
+      <c r="S27" t="s">
         <v>59</v>
       </c>
-      <c r="R27" t="s">
-        <v>39</v>
-      </c>
-      <c r="S27" t="s">
+      <c r="T27" t="s">
+        <v>40</v>
+      </c>
+      <c r="U27" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>212</v>
+        <v>232</v>
       </c>
       <c r="B28" t="s">
-        <v>213</v>
+        <v>233</v>
       </c>
       <c r="C28" t="s">
         <v>32</v>
@@ -2733,171 +3131,709 @@
         <v>22</v>
       </c>
       <c r="E28" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F28" t="s">
-        <v>23</v>
+        <v>151</v>
       </c>
       <c r="G28" t="s">
-        <v>195</v>
+        <v>234</v>
       </c>
       <c r="H28" t="s">
-        <v>214</v>
+        <v>173</v>
       </c>
       <c r="I28" t="s">
-        <v>196</v>
+        <v>21</v>
       </c>
       <c r="J28" t="s">
-        <v>19</v>
+        <v>237</v>
       </c>
       <c r="K28" t="s">
-        <v>217</v>
+        <v>88</v>
       </c>
       <c r="L28" t="s">
-        <v>47</v>
+        <v>89</v>
       </c>
       <c r="M28" t="s">
-        <v>27</v>
+        <v>238</v>
       </c>
       <c r="N28" t="s">
-        <v>216</v>
+        <v>21</v>
       </c>
       <c r="O28" t="s">
-        <v>19</v>
+        <v>235</v>
       </c>
       <c r="P28" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="Q28" t="s">
-        <v>24</v>
+        <v>154</v>
       </c>
       <c r="R28" t="s">
+        <v>236</v>
+      </c>
+      <c r="S28" t="s">
+        <v>86</v>
+      </c>
+      <c r="T28" t="s">
         <v>25</v>
       </c>
-      <c r="S28" t="s">
+      <c r="U28" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>218</v>
+        <v>239</v>
       </c>
       <c r="B29" t="s">
-        <v>219</v>
+        <v>240</v>
       </c>
       <c r="C29" t="s">
-        <v>156</v>
+        <v>32</v>
       </c>
       <c r="D29" t="s">
         <v>33</v>
       </c>
       <c r="E29" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F29" t="s">
+        <v>151</v>
+      </c>
+      <c r="G29" t="s">
+        <v>241</v>
+      </c>
+      <c r="H29" t="s">
+        <v>242</v>
+      </c>
+      <c r="I29" t="s">
+        <v>21</v>
+      </c>
+      <c r="J29" t="s">
+        <v>246</v>
+      </c>
+      <c r="K29" t="s">
+        <v>88</v>
+      </c>
+      <c r="L29" t="s">
+        <v>89</v>
+      </c>
+      <c r="M29" t="s">
+        <v>247</v>
+      </c>
+      <c r="N29" t="s">
+        <v>21</v>
+      </c>
+      <c r="O29" t="s">
+        <v>243</v>
+      </c>
+      <c r="P29" t="s">
+        <v>243</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>244</v>
+      </c>
+      <c r="R29" t="s">
+        <v>21</v>
+      </c>
+      <c r="S29" t="s">
+        <v>245</v>
+      </c>
+      <c r="T29" t="s">
+        <v>40</v>
+      </c>
+      <c r="U29" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>248</v>
+      </c>
+      <c r="B30" t="s">
+        <v>249</v>
+      </c>
+      <c r="C30" t="s">
+        <v>32</v>
+      </c>
+      <c r="D30" t="s">
+        <v>33</v>
+      </c>
+      <c r="E30" t="s">
+        <v>23</v>
+      </c>
+      <c r="F30" t="s">
+        <v>151</v>
+      </c>
+      <c r="G30" t="s">
+        <v>241</v>
+      </c>
+      <c r="H30" t="s">
+        <v>242</v>
+      </c>
+      <c r="I30" t="s">
+        <v>21</v>
+      </c>
+      <c r="J30" t="s">
+        <v>251</v>
+      </c>
+      <c r="K30" t="s">
+        <v>88</v>
+      </c>
+      <c r="L30" t="s">
+        <v>89</v>
+      </c>
+      <c r="M30" t="s">
+        <v>252</v>
+      </c>
+      <c r="N30" t="s">
+        <v>21</v>
+      </c>
+      <c r="O30" t="s">
+        <v>250</v>
+      </c>
+      <c r="P30" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>244</v>
+      </c>
+      <c r="R30" t="s">
+        <v>21</v>
+      </c>
+      <c r="S30" t="s">
+        <v>39</v>
+      </c>
+      <c r="T30" t="s">
+        <v>40</v>
+      </c>
+      <c r="U30" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>253</v>
+      </c>
+      <c r="B31" t="s">
+        <v>254</v>
+      </c>
+      <c r="C31" t="s">
+        <v>32</v>
+      </c>
+      <c r="D31" t="s">
+        <v>33</v>
+      </c>
+      <c r="E31" t="s">
+        <v>23</v>
+      </c>
+      <c r="F31" t="s">
+        <v>151</v>
+      </c>
+      <c r="G31" t="s">
+        <v>241</v>
+      </c>
+      <c r="H31" t="s">
+        <v>242</v>
+      </c>
+      <c r="I31" t="s">
+        <v>21</v>
+      </c>
+      <c r="J31" t="s">
+        <v>256</v>
+      </c>
+      <c r="K31" t="s">
+        <v>88</v>
+      </c>
+      <c r="L31" t="s">
+        <v>89</v>
+      </c>
+      <c r="M31" t="s">
+        <v>257</v>
+      </c>
+      <c r="N31" t="s">
+        <v>21</v>
+      </c>
+      <c r="O31" t="s">
+        <v>255</v>
+      </c>
+      <c r="P31" t="s">
+        <v>255</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>244</v>
+      </c>
+      <c r="R31" t="s">
+        <v>21</v>
+      </c>
+      <c r="S31" t="s">
+        <v>39</v>
+      </c>
+      <c r="T31" t="s">
+        <v>40</v>
+      </c>
+      <c r="U31" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>258</v>
+      </c>
+      <c r="B32" t="s">
+        <v>259</v>
+      </c>
+      <c r="C32" t="s">
+        <v>32</v>
+      </c>
+      <c r="D32" t="s">
+        <v>33</v>
+      </c>
+      <c r="E32" t="s">
+        <v>23</v>
+      </c>
+      <c r="F32" t="s">
+        <v>260</v>
+      </c>
+      <c r="G32" t="s">
+        <v>241</v>
+      </c>
+      <c r="H32" t="s">
+        <v>242</v>
+      </c>
+      <c r="I32" t="s">
+        <v>21</v>
+      </c>
+      <c r="J32" t="s">
+        <v>262</v>
+      </c>
+      <c r="K32" t="s">
+        <v>88</v>
+      </c>
+      <c r="L32" t="s">
+        <v>89</v>
+      </c>
+      <c r="M32" t="s">
+        <v>263</v>
+      </c>
+      <c r="N32" t="s">
+        <v>21</v>
+      </c>
+      <c r="O32" t="s">
+        <v>261</v>
+      </c>
+      <c r="P32" t="s">
+        <v>261</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>244</v>
+      </c>
+      <c r="R32" t="s">
+        <v>21</v>
+      </c>
+      <c r="S32" t="s">
+        <v>59</v>
+      </c>
+      <c r="T32" t="s">
+        <v>40</v>
+      </c>
+      <c r="U32" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>264</v>
+      </c>
+      <c r="B33" t="s">
+        <v>265</v>
+      </c>
+      <c r="C33" t="s">
+        <v>32</v>
+      </c>
+      <c r="D33" t="s">
+        <v>33</v>
+      </c>
+      <c r="E33" t="s">
         <v>34</v>
       </c>
-      <c r="G29" t="s">
-        <v>220</v>
-      </c>
-      <c r="H29" t="s">
-        <v>191</v>
-      </c>
-      <c r="I29" t="s">
-        <v>221</v>
-      </c>
-      <c r="J29" t="s">
-        <v>221</v>
-      </c>
-      <c r="K29" t="s">
-        <v>223</v>
-      </c>
-      <c r="L29" t="s">
-        <v>47</v>
-      </c>
-      <c r="M29" t="s">
-        <v>28</v>
-      </c>
-      <c r="N29" t="s">
-        <v>224</v>
-      </c>
-      <c r="O29" t="s">
-        <v>19</v>
-      </c>
-      <c r="P29" t="s">
-        <v>222</v>
-      </c>
-      <c r="Q29" t="s">
-        <v>38</v>
-      </c>
-      <c r="R29" t="s">
-        <v>39</v>
-      </c>
-      <c r="S29" t="s">
+      <c r="F33" t="s">
+        <v>266</v>
+      </c>
+      <c r="G33" t="s">
+        <v>267</v>
+      </c>
+      <c r="H33" t="s">
+        <v>21</v>
+      </c>
+      <c r="I33" t="s">
+        <v>21</v>
+      </c>
+      <c r="J33" t="s">
+        <v>270</v>
+      </c>
+      <c r="K33" t="s">
+        <v>88</v>
+      </c>
+      <c r="L33" t="s">
+        <v>89</v>
+      </c>
+      <c r="M33" t="s">
+        <v>271</v>
+      </c>
+      <c r="N33" t="s">
+        <v>21</v>
+      </c>
+      <c r="O33" t="s">
+        <v>268</v>
+      </c>
+      <c r="P33" t="s">
+        <v>268</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>269</v>
+      </c>
+      <c r="R33" t="s">
+        <v>21</v>
+      </c>
+      <c r="S33" t="s">
+        <v>59</v>
+      </c>
+      <c r="T33" t="s">
+        <v>40</v>
+      </c>
+      <c r="U33" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
-        <v>225</v>
-      </c>
-      <c r="B30" t="s">
-        <v>226</v>
-      </c>
-      <c r="C30" t="s">
-        <v>20</v>
-      </c>
-      <c r="D30" t="s">
+    <row r="34" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>272</v>
+      </c>
+      <c r="B34" t="s">
+        <v>273</v>
+      </c>
+      <c r="C34" t="s">
+        <v>172</v>
+      </c>
+      <c r="D34" t="s">
         <v>22</v>
       </c>
-      <c r="E30" t="s">
+      <c r="E34" t="s">
+        <v>23</v>
+      </c>
+      <c r="F34" t="s">
+        <v>151</v>
+      </c>
+      <c r="G34" t="s">
+        <v>274</v>
+      </c>
+      <c r="H34" t="s">
+        <v>94</v>
+      </c>
+      <c r="I34" t="s">
+        <v>160</v>
+      </c>
+      <c r="J34" t="s">
+        <v>277</v>
+      </c>
+      <c r="K34" t="s">
+        <v>88</v>
+      </c>
+      <c r="L34" t="s">
+        <v>27</v>
+      </c>
+      <c r="M34" t="s">
+        <v>276</v>
+      </c>
+      <c r="N34" t="s">
+        <v>21</v>
+      </c>
+      <c r="O34" t="s">
+        <v>275</v>
+      </c>
+      <c r="P34" t="s">
+        <v>275</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>154</v>
+      </c>
+      <c r="R34" t="s">
+        <v>21</v>
+      </c>
+      <c r="S34" t="s">
+        <v>24</v>
+      </c>
+      <c r="T34" t="s">
+        <v>25</v>
+      </c>
+      <c r="U34" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>278</v>
+      </c>
+      <c r="B35" t="s">
+        <v>279</v>
+      </c>
+      <c r="C35" t="s">
+        <v>172</v>
+      </c>
+      <c r="D35" t="s">
         <v>22</v>
       </c>
-      <c r="F30" t="s">
+      <c r="E35" t="s">
         <v>23</v>
       </c>
-      <c r="G30" t="s">
-        <v>227</v>
-      </c>
-      <c r="H30" t="s">
-        <v>228</v>
-      </c>
-      <c r="I30" t="s">
-        <v>19</v>
-      </c>
-      <c r="J30" t="s">
-        <v>19</v>
-      </c>
-      <c r="K30" t="s">
-        <v>230</v>
-      </c>
-      <c r="L30" t="s">
-        <v>47</v>
-      </c>
-      <c r="M30" t="s">
+      <c r="F35" t="s">
+        <v>151</v>
+      </c>
+      <c r="G35" t="s">
+        <v>280</v>
+      </c>
+      <c r="H35" t="s">
+        <v>281</v>
+      </c>
+      <c r="I35" t="s">
+        <v>173</v>
+      </c>
+      <c r="J35" t="s">
+        <v>283</v>
+      </c>
+      <c r="K35" t="s">
+        <v>88</v>
+      </c>
+      <c r="L35" t="s">
         <v>27</v>
       </c>
-      <c r="N30" t="s">
-        <v>231</v>
-      </c>
-      <c r="O30" t="s">
-        <v>19</v>
-      </c>
-      <c r="P30" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q30" t="s">
-        <v>92</v>
-      </c>
-      <c r="R30" t="s">
-        <v>93</v>
-      </c>
-      <c r="S30" t="s">
+      <c r="M35" t="s">
+        <v>284</v>
+      </c>
+      <c r="N35" t="s">
+        <v>21</v>
+      </c>
+      <c r="O35" t="s">
+        <v>282</v>
+      </c>
+      <c r="P35" t="s">
+        <v>282</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>154</v>
+      </c>
+      <c r="R35" t="s">
+        <v>21</v>
+      </c>
+      <c r="S35" t="s">
+        <v>24</v>
+      </c>
+      <c r="T35" t="s">
+        <v>25</v>
+      </c>
+      <c r="U35" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>285</v>
+      </c>
+      <c r="B36" t="s">
+        <v>286</v>
+      </c>
+      <c r="C36" t="s">
+        <v>172</v>
+      </c>
+      <c r="D36" t="s">
+        <v>22</v>
+      </c>
+      <c r="E36" t="s">
+        <v>23</v>
+      </c>
+      <c r="F36" t="s">
+        <v>287</v>
+      </c>
+      <c r="G36" t="s">
+        <v>36</v>
+      </c>
+      <c r="H36" t="s">
+        <v>160</v>
+      </c>
+      <c r="I36" t="s">
+        <v>175</v>
+      </c>
+      <c r="J36" t="s">
+        <v>290</v>
+      </c>
+      <c r="K36" t="s">
+        <v>88</v>
+      </c>
+      <c r="L36" t="s">
+        <v>27</v>
+      </c>
+      <c r="M36" t="s">
+        <v>291</v>
+      </c>
+      <c r="N36" t="s">
+        <v>21</v>
+      </c>
+      <c r="O36" t="s">
+        <v>288</v>
+      </c>
+      <c r="P36" t="s">
+        <v>288</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>289</v>
+      </c>
+      <c r="R36" t="s">
+        <v>21</v>
+      </c>
+      <c r="S36" t="s">
+        <v>24</v>
+      </c>
+      <c r="T36" t="s">
+        <v>25</v>
+      </c>
+      <c r="U36" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>292</v>
+      </c>
+      <c r="B37" t="s">
+        <v>293</v>
+      </c>
+      <c r="C37" t="s">
+        <v>172</v>
+      </c>
+      <c r="D37" t="s">
+        <v>22</v>
+      </c>
+      <c r="E37" t="s">
+        <v>23</v>
+      </c>
+      <c r="F37" t="s">
+        <v>294</v>
+      </c>
+      <c r="G37" t="s">
+        <v>295</v>
+      </c>
+      <c r="H37" t="s">
+        <v>160</v>
+      </c>
+      <c r="I37" t="s">
+        <v>175</v>
+      </c>
+      <c r="J37" t="s">
+        <v>298</v>
+      </c>
+      <c r="K37" t="s">
+        <v>88</v>
+      </c>
+      <c r="L37" t="s">
+        <v>27</v>
+      </c>
+      <c r="M37" t="s">
+        <v>299</v>
+      </c>
+      <c r="N37" t="s">
+        <v>21</v>
+      </c>
+      <c r="O37" t="s">
+        <v>296</v>
+      </c>
+      <c r="P37" t="s">
+        <v>296</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>297</v>
+      </c>
+      <c r="R37" t="s">
+        <v>21</v>
+      </c>
+      <c r="S37" t="s">
+        <v>24</v>
+      </c>
+      <c r="T37" t="s">
+        <v>25</v>
+      </c>
+      <c r="U37" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>300</v>
+      </c>
+      <c r="B38" t="s">
+        <v>301</v>
+      </c>
+      <c r="C38" t="s">
+        <v>32</v>
+      </c>
+      <c r="D38" t="s">
+        <v>33</v>
+      </c>
+      <c r="E38" t="s">
+        <v>23</v>
+      </c>
+      <c r="F38" t="s">
+        <v>302</v>
+      </c>
+      <c r="G38" t="s">
+        <v>303</v>
+      </c>
+      <c r="H38" t="s">
+        <v>304</v>
+      </c>
+      <c r="I38" t="s">
+        <v>21</v>
+      </c>
+      <c r="J38" t="s">
+        <v>307</v>
+      </c>
+      <c r="K38" t="s">
+        <v>29</v>
+      </c>
+      <c r="L38" t="s">
+        <v>27</v>
+      </c>
+      <c r="M38" t="s">
+        <v>308</v>
+      </c>
+      <c r="N38" t="s">
+        <v>21</v>
+      </c>
+      <c r="O38" t="s">
+        <v>305</v>
+      </c>
+      <c r="P38" t="s">
+        <v>305</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>306</v>
+      </c>
+      <c r="R38" t="s">
+        <v>21</v>
+      </c>
+      <c r="S38" t="s">
+        <v>59</v>
+      </c>
+      <c r="T38" t="s">
+        <v>40</v>
+      </c>
+      <c r="U38" t="s">
         <v>26</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S30"/>
+  <autoFilter ref="A1:U38"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/transfert.xlsx
+++ b/transfert.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Données du dasboard" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Données du dasboard'!$A$1:$U$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Données du dasboard'!$A$1:$U$37</definedName>
     <definedName name="corbeil">#REF!</definedName>
     <definedName name="corbeilHeader">#REF!</definedName>
     <definedName name="en_tete">#REF!</definedName>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="798" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="299">
   <si>
     <t>ID DOSSIER</t>
   </si>
@@ -266,45 +266,15 @@
     <t>26/06/2026 14:35:28</t>
   </si>
   <si>
-    <t>65442117</t>
-  </si>
-  <si>
-    <t>25/06/2026 08:37:15</t>
-  </si>
-  <si>
-    <t>DOUANES</t>
-  </si>
-  <si>
-    <t>ABIDJAN-PORT-BOUET//VOIE INCONNUE/AEROPORT FRET DOUANES</t>
-  </si>
-  <si>
-    <t>50M</t>
-  </si>
-  <si>
-    <t>VPNLL230023</t>
-  </si>
-  <si>
-    <t>0709602414</t>
-  </si>
-  <si>
-    <t>1959236</t>
-  </si>
-  <si>
     <t>IP Connect LL</t>
   </si>
   <si>
-    <t>66580530</t>
-  </si>
-  <si>
     <t>Offert</t>
   </si>
   <si>
     <t>BBF : Prerequis Etude</t>
   </si>
   <si>
-    <t>15/07/2026 10:11:02</t>
-  </si>
-  <si>
     <t>65530820</t>
   </si>
   <si>
@@ -957,9 +927,6 @@
   </si>
   <si>
     <t>18/09/2026 15:15:42</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BBF : Prerequis Etude : </t>
   </si>
 </sst>
 </file>
@@ -1336,7 +1303,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U38"/>
+  <dimension ref="A1:U37"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" style="1" bestFit="1" customWidth="1"/>
@@ -1884,10 +1851,10 @@
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B9" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C9" t="s">
         <v>32</v>
@@ -1899,13 +1866,13 @@
         <v>23</v>
       </c>
       <c r="F9" t="s">
-        <v>80</v>
+        <v>35</v>
       </c>
       <c r="G9" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H9" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I9" t="s">
         <v>21</v>
@@ -1914,31 +1881,31 @@
         <v>87</v>
       </c>
       <c r="K9" t="s">
-        <v>88</v>
+        <v>29</v>
       </c>
       <c r="L9" t="s">
-        <v>309</v>
+        <v>42</v>
       </c>
       <c r="M9" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="N9" t="s">
         <v>21</v>
       </c>
       <c r="O9" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="P9" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="Q9" t="s">
-        <v>84</v>
+        <v>38</v>
       </c>
       <c r="R9" t="s">
-        <v>85</v>
+        <v>21</v>
       </c>
       <c r="S9" t="s">
-        <v>86</v>
+        <v>24</v>
       </c>
       <c r="T9" t="s">
         <v>25</v>
@@ -1949,10 +1916,10 @@
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B10" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C10" t="s">
         <v>32</v>
@@ -1967,16 +1934,16 @@
         <v>35</v>
       </c>
       <c r="G10" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="H10" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="I10" t="s">
         <v>21</v>
       </c>
       <c r="J10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K10" t="s">
         <v>29</v>
@@ -1985,16 +1952,16 @@
         <v>42</v>
       </c>
       <c r="M10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N10" t="s">
         <v>21</v>
       </c>
       <c r="O10" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="P10" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="Q10" t="s">
         <v>38</v>
@@ -2003,10 +1970,10 @@
         <v>21</v>
       </c>
       <c r="S10" t="s">
-        <v>24</v>
+        <v>93</v>
       </c>
       <c r="T10" t="s">
-        <v>25</v>
+        <v>94</v>
       </c>
       <c r="U10" t="s">
         <v>26</v>
@@ -2014,10 +1981,10 @@
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
+        <v>97</v>
+      </c>
+      <c r="B11" t="s">
         <v>98</v>
-      </c>
-      <c r="B11" t="s">
-        <v>99</v>
       </c>
       <c r="C11" t="s">
         <v>32</v>
@@ -2032,16 +1999,16 @@
         <v>35</v>
       </c>
       <c r="G11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H11" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I11" t="s">
         <v>21</v>
       </c>
       <c r="J11" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="K11" t="s">
         <v>29</v>
@@ -2050,28 +2017,28 @@
         <v>42</v>
       </c>
       <c r="M11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="N11" t="s">
         <v>21</v>
       </c>
       <c r="O11" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="P11" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="Q11" t="s">
         <v>38</v>
       </c>
       <c r="R11" t="s">
-        <v>21</v>
+        <v>101</v>
       </c>
       <c r="S11" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T11" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="U11" t="s">
         <v>26</v>
@@ -2079,10 +2046,10 @@
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B12" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C12" t="s">
         <v>32</v>
@@ -2097,16 +2064,16 @@
         <v>35</v>
       </c>
       <c r="G12" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="H12" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="I12" t="s">
         <v>21</v>
       </c>
       <c r="J12" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="K12" t="s">
         <v>29</v>
@@ -2115,28 +2082,28 @@
         <v>42</v>
       </c>
       <c r="M12" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="N12" t="s">
         <v>21</v>
       </c>
       <c r="O12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="P12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Q12" t="s">
         <v>38</v>
       </c>
       <c r="R12" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="S12" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="T12" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="U12" t="s">
         <v>26</v>
@@ -2144,10 +2111,10 @@
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B13" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C13" t="s">
         <v>32</v>
@@ -2162,16 +2129,16 @@
         <v>35</v>
       </c>
       <c r="G13" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="H13" t="s">
+        <v>84</v>
+      </c>
+      <c r="I13" t="s">
+        <v>21</v>
+      </c>
+      <c r="J13" t="s">
         <v>117</v>
-      </c>
-      <c r="I13" t="s">
-        <v>21</v>
-      </c>
-      <c r="J13" t="s">
-        <v>120</v>
       </c>
       <c r="K13" t="s">
         <v>29</v>
@@ -2180,28 +2147,28 @@
         <v>42</v>
       </c>
       <c r="M13" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="N13" t="s">
         <v>21</v>
       </c>
       <c r="O13" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="P13" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="Q13" t="s">
         <v>38</v>
       </c>
       <c r="R13" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="S13" t="s">
-        <v>112</v>
+        <v>78</v>
       </c>
       <c r="T13" t="s">
-        <v>104</v>
+        <v>25</v>
       </c>
       <c r="U13" t="s">
         <v>26</v>
@@ -2209,10 +2176,10 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B14" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C14" t="s">
         <v>32</v>
@@ -2227,16 +2194,16 @@
         <v>35</v>
       </c>
       <c r="G14" t="s">
+        <v>114</v>
+      </c>
+      <c r="H14" t="s">
+        <v>91</v>
+      </c>
+      <c r="I14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J14" t="s">
         <v>124</v>
-      </c>
-      <c r="H14" t="s">
-        <v>94</v>
-      </c>
-      <c r="I14" t="s">
-        <v>21</v>
-      </c>
-      <c r="J14" t="s">
-        <v>127</v>
       </c>
       <c r="K14" t="s">
         <v>29</v>
@@ -2245,25 +2212,25 @@
         <v>42</v>
       </c>
       <c r="M14" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="N14" t="s">
         <v>21</v>
       </c>
       <c r="O14" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="P14" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="Q14" t="s">
         <v>38</v>
       </c>
       <c r="R14" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="S14" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="T14" t="s">
         <v>25</v>
@@ -2274,10 +2241,10 @@
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B15" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C15" t="s">
         <v>32</v>
@@ -2292,16 +2259,16 @@
         <v>35</v>
       </c>
       <c r="G15" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="H15" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I15" t="s">
         <v>21</v>
       </c>
       <c r="J15" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="K15" t="s">
         <v>29</v>
@@ -2310,25 +2277,25 @@
         <v>42</v>
       </c>
       <c r="M15" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="N15" t="s">
         <v>21</v>
       </c>
       <c r="O15" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="P15" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="Q15" t="s">
         <v>38</v>
       </c>
       <c r="R15" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="S15" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="T15" t="s">
         <v>25</v>
@@ -2339,64 +2306,64 @@
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B16" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C16" t="s">
         <v>32</v>
       </c>
       <c r="D16" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="E16" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="F16" t="s">
-        <v>35</v>
+        <v>133</v>
       </c>
       <c r="G16" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="H16" t="s">
-        <v>101</v>
+        <v>21</v>
       </c>
       <c r="I16" t="s">
         <v>21</v>
       </c>
       <c r="J16" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="K16" t="s">
-        <v>29</v>
+        <v>79</v>
       </c>
       <c r="L16" t="s">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="M16" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="N16" t="s">
         <v>21</v>
       </c>
       <c r="O16" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="P16" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="Q16" t="s">
-        <v>38</v>
+        <v>136</v>
       </c>
       <c r="R16" t="s">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="S16" t="s">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="T16" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="U16" t="s">
         <v>26</v>
@@ -2404,28 +2371,28 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B17" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C17" t="s">
         <v>32</v>
       </c>
       <c r="D17" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="E17" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="F17" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G17" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="H17" t="s">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="I17" t="s">
         <v>21</v>
@@ -2434,34 +2401,34 @@
         <v>147</v>
       </c>
       <c r="K17" t="s">
-        <v>88</v>
+        <v>29</v>
       </c>
       <c r="L17" t="s">
-        <v>89</v>
+        <v>42</v>
       </c>
       <c r="M17" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="N17" t="s">
         <v>21</v>
       </c>
       <c r="O17" t="s">
+        <v>143</v>
+      </c>
+      <c r="P17" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>144</v>
+      </c>
+      <c r="R17" t="s">
         <v>145</v>
       </c>
-      <c r="P17" t="s">
-        <v>145</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>146</v>
-      </c>
-      <c r="R17" t="s">
-        <v>21</v>
-      </c>
       <c r="S17" t="s">
-        <v>59</v>
+        <v>102</v>
       </c>
       <c r="T17" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="U17" t="s">
         <v>26</v>
@@ -2469,10 +2436,10 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
+        <v>148</v>
+      </c>
+      <c r="B18" t="s">
         <v>149</v>
-      </c>
-      <c r="B18" t="s">
-        <v>150</v>
       </c>
       <c r="C18" t="s">
         <v>32</v>
@@ -2484,19 +2451,19 @@
         <v>23</v>
       </c>
       <c r="F18" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="G18" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="H18" t="s">
-        <v>117</v>
+        <v>150</v>
       </c>
       <c r="I18" t="s">
         <v>21</v>
       </c>
       <c r="J18" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="K18" t="s">
         <v>29</v>
@@ -2505,28 +2472,28 @@
         <v>42</v>
       </c>
       <c r="M18" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="N18" t="s">
         <v>21</v>
       </c>
       <c r="O18" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="P18" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="Q18" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="R18" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="S18" t="s">
-        <v>112</v>
+        <v>78</v>
       </c>
       <c r="T18" t="s">
-        <v>104</v>
+        <v>25</v>
       </c>
       <c r="U18" t="s">
         <v>26</v>
@@ -2534,10 +2501,10 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B19" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C19" t="s">
         <v>32</v>
@@ -2549,19 +2516,19 @@
         <v>23</v>
       </c>
       <c r="F19" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="G19" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="H19" t="s">
+        <v>157</v>
+      </c>
+      <c r="I19" t="s">
+        <v>21</v>
+      </c>
+      <c r="J19" t="s">
         <v>160</v>
-      </c>
-      <c r="I19" t="s">
-        <v>21</v>
-      </c>
-      <c r="J19" t="s">
-        <v>163</v>
       </c>
       <c r="K19" t="s">
         <v>29</v>
@@ -2570,25 +2537,25 @@
         <v>42</v>
       </c>
       <c r="M19" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="N19" t="s">
         <v>21</v>
       </c>
       <c r="O19" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="P19" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="Q19" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="R19" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="S19" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="T19" t="s">
         <v>25</v>
@@ -2599,10 +2566,10 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B20" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C20" t="s">
         <v>32</v>
@@ -2614,46 +2581,46 @@
         <v>23</v>
       </c>
       <c r="F20" t="s">
-        <v>151</v>
+        <v>168</v>
       </c>
       <c r="G20" t="s">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="H20" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="I20" t="s">
         <v>21</v>
       </c>
       <c r="J20" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="K20" t="s">
-        <v>29</v>
+        <v>79</v>
       </c>
       <c r="L20" t="s">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="M20" t="s">
+        <v>175</v>
+      </c>
+      <c r="N20" t="s">
+        <v>21</v>
+      </c>
+      <c r="O20" t="s">
         <v>171</v>
       </c>
-      <c r="N20" t="s">
-        <v>21</v>
-      </c>
-      <c r="O20" t="s">
-        <v>168</v>
-      </c>
       <c r="P20" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="Q20" t="s">
-        <v>154</v>
+        <v>172</v>
       </c>
       <c r="R20" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="S20" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="T20" t="s">
         <v>25</v>
@@ -2679,60 +2646,60 @@
         <v>23</v>
       </c>
       <c r="F21" t="s">
+        <v>168</v>
+      </c>
+      <c r="G21" t="s">
+        <v>169</v>
+      </c>
+      <c r="H21" t="s">
+        <v>170</v>
+      </c>
+      <c r="I21" t="s">
+        <v>21</v>
+      </c>
+      <c r="J21" t="s">
+        <v>180</v>
+      </c>
+      <c r="K21" t="s">
+        <v>79</v>
+      </c>
+      <c r="L21" t="s">
+        <v>80</v>
+      </c>
+      <c r="M21" t="s">
+        <v>181</v>
+      </c>
+      <c r="N21" t="s">
+        <v>21</v>
+      </c>
+      <c r="O21" t="s">
         <v>178</v>
       </c>
-      <c r="G21" t="s">
+      <c r="P21" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>172</v>
+      </c>
+      <c r="R21" t="s">
         <v>179</v>
       </c>
-      <c r="H21" t="s">
-        <v>180</v>
-      </c>
-      <c r="I21" t="s">
-        <v>21</v>
-      </c>
-      <c r="J21" t="s">
-        <v>184</v>
-      </c>
-      <c r="K21" t="s">
-        <v>88</v>
-      </c>
-      <c r="L21" t="s">
-        <v>89</v>
-      </c>
-      <c r="M21" t="s">
-        <v>185</v>
-      </c>
-      <c r="N21" t="s">
-        <v>21</v>
-      </c>
-      <c r="O21" t="s">
-        <v>181</v>
-      </c>
-      <c r="P21" t="s">
-        <v>181</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>182</v>
-      </c>
-      <c r="R21" t="s">
-        <v>183</v>
-      </c>
       <c r="S21" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="T21" t="s">
         <v>25</v>
       </c>
       <c r="U21" t="s">
-        <v>26</v>
+        <v>164</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B22" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C22" t="s">
         <v>32</v>
@@ -2744,60 +2711,60 @@
         <v>23</v>
       </c>
       <c r="F22" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="G22" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="H22" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="I22" t="s">
         <v>21</v>
       </c>
       <c r="J22" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="K22" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="L22" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="M22" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="N22" t="s">
         <v>21</v>
       </c>
       <c r="O22" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="P22" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="Q22" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="R22" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="S22" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="T22" t="s">
         <v>25</v>
       </c>
       <c r="U22" t="s">
-        <v>174</v>
+        <v>26</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="B23" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C23" t="s">
         <v>32</v>
@@ -2809,60 +2776,60 @@
         <v>23</v>
       </c>
       <c r="F23" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="G23" t="s">
+        <v>184</v>
+      </c>
+      <c r="H23" t="s">
+        <v>170</v>
+      </c>
+      <c r="I23" t="s">
+        <v>21</v>
+      </c>
+      <c r="J23" t="s">
+        <v>193</v>
+      </c>
+      <c r="K23" t="s">
+        <v>79</v>
+      </c>
+      <c r="L23" t="s">
+        <v>80</v>
+      </c>
+      <c r="M23" t="s">
         <v>194</v>
       </c>
-      <c r="H23" t="s">
-        <v>180</v>
-      </c>
-      <c r="I23" t="s">
-        <v>21</v>
-      </c>
-      <c r="J23" t="s">
-        <v>197</v>
-      </c>
-      <c r="K23" t="s">
-        <v>88</v>
-      </c>
-      <c r="L23" t="s">
-        <v>89</v>
-      </c>
-      <c r="M23" t="s">
-        <v>198</v>
-      </c>
       <c r="N23" t="s">
         <v>21</v>
       </c>
       <c r="O23" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="P23" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="Q23" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="R23" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="S23" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="T23" t="s">
         <v>25</v>
       </c>
       <c r="U23" t="s">
-        <v>26</v>
+        <v>164</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="B24" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C24" t="s">
         <v>32</v>
@@ -2874,13 +2841,13 @@
         <v>23</v>
       </c>
       <c r="F24" t="s">
-        <v>178</v>
+        <v>197</v>
       </c>
       <c r="G24" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="H24" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="I24" t="s">
         <v>21</v>
@@ -2889,10 +2856,10 @@
         <v>203</v>
       </c>
       <c r="K24" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="L24" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="M24" t="s">
         <v>204</v>
@@ -2901,25 +2868,25 @@
         <v>21</v>
       </c>
       <c r="O24" t="s">
+        <v>200</v>
+      </c>
+      <c r="P24" t="s">
+        <v>200</v>
+      </c>
+      <c r="Q24" t="s">
         <v>201</v>
-      </c>
-      <c r="P24" t="s">
-        <v>201</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>182</v>
       </c>
       <c r="R24" t="s">
         <v>202</v>
       </c>
       <c r="S24" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="T24" t="s">
         <v>25</v>
       </c>
       <c r="U24" t="s">
-        <v>174</v>
+        <v>26</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.35">
@@ -2945,43 +2912,43 @@
         <v>208</v>
       </c>
       <c r="H25" t="s">
+        <v>150</v>
+      </c>
+      <c r="I25" t="s">
+        <v>21</v>
+      </c>
+      <c r="J25" t="s">
+        <v>212</v>
+      </c>
+      <c r="K25" t="s">
+        <v>79</v>
+      </c>
+      <c r="L25" t="s">
+        <v>80</v>
+      </c>
+      <c r="M25" t="s">
+        <v>213</v>
+      </c>
+      <c r="N25" t="s">
+        <v>21</v>
+      </c>
+      <c r="O25" t="s">
         <v>209</v>
       </c>
-      <c r="I25" t="s">
-        <v>21</v>
-      </c>
-      <c r="J25" t="s">
-        <v>213</v>
-      </c>
-      <c r="K25" t="s">
-        <v>88</v>
-      </c>
-      <c r="L25" t="s">
-        <v>89</v>
-      </c>
-      <c r="M25" t="s">
-        <v>214</v>
-      </c>
-      <c r="N25" t="s">
-        <v>21</v>
-      </c>
-      <c r="O25" t="s">
+      <c r="P25" t="s">
+        <v>209</v>
+      </c>
+      <c r="Q25" t="s">
         <v>210</v>
       </c>
-      <c r="P25" t="s">
-        <v>210</v>
-      </c>
-      <c r="Q25" t="s">
+      <c r="R25" t="s">
         <v>211</v>
       </c>
-      <c r="R25" t="s">
-        <v>212</v>
-      </c>
       <c r="S25" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="T25" t="s">
-        <v>25</v>
+        <v>94</v>
       </c>
       <c r="U25" t="s">
         <v>26</v>
@@ -2989,64 +2956,64 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
+        <v>214</v>
+      </c>
+      <c r="B26" t="s">
         <v>215</v>
-      </c>
-      <c r="B26" t="s">
-        <v>216</v>
       </c>
       <c r="C26" t="s">
         <v>32</v>
       </c>
       <c r="D26" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="E26" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="F26" t="s">
+        <v>216</v>
+      </c>
+      <c r="G26" t="s">
         <v>217</v>
       </c>
-      <c r="G26" t="s">
+      <c r="H26" t="s">
+        <v>21</v>
+      </c>
+      <c r="I26" t="s">
+        <v>21</v>
+      </c>
+      <c r="J26" t="s">
+        <v>220</v>
+      </c>
+      <c r="K26" t="s">
+        <v>79</v>
+      </c>
+      <c r="L26" t="s">
+        <v>28</v>
+      </c>
+      <c r="M26" t="s">
+        <v>221</v>
+      </c>
+      <c r="N26" t="s">
+        <v>21</v>
+      </c>
+      <c r="O26" t="s">
         <v>218</v>
       </c>
-      <c r="H26" t="s">
-        <v>160</v>
-      </c>
-      <c r="I26" t="s">
-        <v>21</v>
-      </c>
-      <c r="J26" t="s">
-        <v>222</v>
-      </c>
-      <c r="K26" t="s">
-        <v>88</v>
-      </c>
-      <c r="L26" t="s">
-        <v>89</v>
-      </c>
-      <c r="M26" t="s">
-        <v>223</v>
-      </c>
-      <c r="N26" t="s">
-        <v>21</v>
-      </c>
-      <c r="O26" t="s">
+      <c r="P26" t="s">
+        <v>218</v>
+      </c>
+      <c r="Q26" t="s">
         <v>219</v>
       </c>
-      <c r="P26" t="s">
-        <v>219</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>220</v>
-      </c>
       <c r="R26" t="s">
-        <v>221</v>
+        <v>21</v>
       </c>
       <c r="S26" t="s">
-        <v>112</v>
+        <v>59</v>
       </c>
       <c r="T26" t="s">
-        <v>104</v>
+        <v>40</v>
       </c>
       <c r="U26" t="s">
         <v>26</v>
@@ -3054,64 +3021,64 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B27" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C27" t="s">
         <v>32</v>
       </c>
       <c r="D27" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="E27" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="F27" t="s">
+        <v>141</v>
+      </c>
+      <c r="G27" t="s">
+        <v>224</v>
+      </c>
+      <c r="H27" t="s">
+        <v>163</v>
+      </c>
+      <c r="I27" t="s">
+        <v>21</v>
+      </c>
+      <c r="J27" t="s">
+        <v>227</v>
+      </c>
+      <c r="K27" t="s">
+        <v>79</v>
+      </c>
+      <c r="L27" t="s">
+        <v>80</v>
+      </c>
+      <c r="M27" t="s">
+        <v>228</v>
+      </c>
+      <c r="N27" t="s">
+        <v>21</v>
+      </c>
+      <c r="O27" t="s">
+        <v>225</v>
+      </c>
+      <c r="P27" t="s">
+        <v>225</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>144</v>
+      </c>
+      <c r="R27" t="s">
         <v>226</v>
       </c>
-      <c r="G27" t="s">
-        <v>227</v>
-      </c>
-      <c r="H27" t="s">
-        <v>21</v>
-      </c>
-      <c r="I27" t="s">
-        <v>21</v>
-      </c>
-      <c r="J27" t="s">
-        <v>230</v>
-      </c>
-      <c r="K27" t="s">
-        <v>88</v>
-      </c>
-      <c r="L27" t="s">
-        <v>28</v>
-      </c>
-      <c r="M27" t="s">
-        <v>231</v>
-      </c>
-      <c r="N27" t="s">
-        <v>21</v>
-      </c>
-      <c r="O27" t="s">
-        <v>228</v>
-      </c>
-      <c r="P27" t="s">
-        <v>228</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>229</v>
-      </c>
-      <c r="R27" t="s">
-        <v>21</v>
-      </c>
       <c r="S27" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="T27" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="U27" t="s">
         <v>26</v>
@@ -3119,64 +3086,64 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B28" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C28" t="s">
         <v>32</v>
       </c>
       <c r="D28" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="E28" t="s">
         <v>23</v>
       </c>
       <c r="F28" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="G28" t="s">
+        <v>231</v>
+      </c>
+      <c r="H28" t="s">
+        <v>232</v>
+      </c>
+      <c r="I28" t="s">
+        <v>21</v>
+      </c>
+      <c r="J28" t="s">
+        <v>236</v>
+      </c>
+      <c r="K28" t="s">
+        <v>79</v>
+      </c>
+      <c r="L28" t="s">
+        <v>80</v>
+      </c>
+      <c r="M28" t="s">
+        <v>237</v>
+      </c>
+      <c r="N28" t="s">
+        <v>21</v>
+      </c>
+      <c r="O28" t="s">
+        <v>233</v>
+      </c>
+      <c r="P28" t="s">
+        <v>233</v>
+      </c>
+      <c r="Q28" t="s">
         <v>234</v>
       </c>
-      <c r="H28" t="s">
-        <v>173</v>
-      </c>
-      <c r="I28" t="s">
-        <v>21</v>
-      </c>
-      <c r="J28" t="s">
-        <v>237</v>
-      </c>
-      <c r="K28" t="s">
-        <v>88</v>
-      </c>
-      <c r="L28" t="s">
-        <v>89</v>
-      </c>
-      <c r="M28" t="s">
-        <v>238</v>
-      </c>
-      <c r="N28" t="s">
-        <v>21</v>
-      </c>
-      <c r="O28" t="s">
+      <c r="R28" t="s">
+        <v>21</v>
+      </c>
+      <c r="S28" t="s">
         <v>235</v>
       </c>
-      <c r="P28" t="s">
-        <v>235</v>
-      </c>
-      <c r="Q28" t="s">
-        <v>154</v>
-      </c>
-      <c r="R28" t="s">
-        <v>236</v>
-      </c>
-      <c r="S28" t="s">
-        <v>86</v>
-      </c>
       <c r="T28" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="U28" t="s">
         <v>26</v>
@@ -3184,10 +3151,10 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
+        <v>238</v>
+      </c>
+      <c r="B29" t="s">
         <v>239</v>
-      </c>
-      <c r="B29" t="s">
-        <v>240</v>
       </c>
       <c r="C29" t="s">
         <v>32</v>
@@ -3199,46 +3166,46 @@
         <v>23</v>
       </c>
       <c r="F29" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="G29" t="s">
+        <v>231</v>
+      </c>
+      <c r="H29" t="s">
+        <v>232</v>
+      </c>
+      <c r="I29" t="s">
+        <v>21</v>
+      </c>
+      <c r="J29" t="s">
         <v>241</v>
       </c>
-      <c r="H29" t="s">
+      <c r="K29" t="s">
+        <v>79</v>
+      </c>
+      <c r="L29" t="s">
+        <v>80</v>
+      </c>
+      <c r="M29" t="s">
         <v>242</v>
       </c>
-      <c r="I29" t="s">
-        <v>21</v>
-      </c>
-      <c r="J29" t="s">
-        <v>246</v>
-      </c>
-      <c r="K29" t="s">
-        <v>88</v>
-      </c>
-      <c r="L29" t="s">
-        <v>89</v>
-      </c>
-      <c r="M29" t="s">
-        <v>247</v>
-      </c>
       <c r="N29" t="s">
         <v>21</v>
       </c>
       <c r="O29" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="P29" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="Q29" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="R29" t="s">
         <v>21</v>
       </c>
       <c r="S29" t="s">
-        <v>245</v>
+        <v>39</v>
       </c>
       <c r="T29" t="s">
         <v>40</v>
@@ -3249,10 +3216,10 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="B30" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="C30" t="s">
         <v>32</v>
@@ -3264,40 +3231,40 @@
         <v>23</v>
       </c>
       <c r="F30" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="G30" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="H30" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="I30" t="s">
         <v>21</v>
       </c>
       <c r="J30" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="K30" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="L30" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="M30" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="N30" t="s">
         <v>21</v>
       </c>
       <c r="O30" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="P30" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="Q30" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="R30" t="s">
         <v>21</v>
@@ -3314,10 +3281,10 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="B31" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="C31" t="s">
         <v>32</v>
@@ -3329,46 +3296,46 @@
         <v>23</v>
       </c>
       <c r="F31" t="s">
-        <v>151</v>
+        <v>250</v>
       </c>
       <c r="G31" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="H31" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="I31" t="s">
         <v>21</v>
       </c>
       <c r="J31" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="K31" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="L31" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="M31" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="N31" t="s">
         <v>21</v>
       </c>
       <c r="O31" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="P31" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="Q31" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="R31" t="s">
         <v>21</v>
       </c>
       <c r="S31" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="T31" t="s">
         <v>40</v>
@@ -3379,10 +3346,10 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="B32" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="C32" t="s">
         <v>32</v>
@@ -3391,43 +3358,43 @@
         <v>33</v>
       </c>
       <c r="E32" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="F32" t="s">
+        <v>256</v>
+      </c>
+      <c r="G32" t="s">
+        <v>257</v>
+      </c>
+      <c r="H32" t="s">
+        <v>21</v>
+      </c>
+      <c r="I32" t="s">
+        <v>21</v>
+      </c>
+      <c r="J32" t="s">
         <v>260</v>
       </c>
-      <c r="G32" t="s">
-        <v>241</v>
-      </c>
-      <c r="H32" t="s">
-        <v>242</v>
-      </c>
-      <c r="I32" t="s">
-        <v>21</v>
-      </c>
-      <c r="J32" t="s">
-        <v>262</v>
-      </c>
       <c r="K32" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="L32" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="M32" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="N32" t="s">
         <v>21</v>
       </c>
       <c r="O32" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="P32" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="Q32" t="s">
-        <v>244</v>
+        <v>259</v>
       </c>
       <c r="R32" t="s">
         <v>21</v>
@@ -3444,64 +3411,64 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
+        <v>262</v>
+      </c>
+      <c r="B33" t="s">
+        <v>263</v>
+      </c>
+      <c r="C33" t="s">
+        <v>162</v>
+      </c>
+      <c r="D33" t="s">
+        <v>22</v>
+      </c>
+      <c r="E33" t="s">
+        <v>23</v>
+      </c>
+      <c r="F33" t="s">
+        <v>141</v>
+      </c>
+      <c r="G33" t="s">
         <v>264</v>
       </c>
-      <c r="B33" t="s">
+      <c r="H33" t="s">
+        <v>84</v>
+      </c>
+      <c r="I33" t="s">
+        <v>150</v>
+      </c>
+      <c r="J33" t="s">
+        <v>267</v>
+      </c>
+      <c r="K33" t="s">
+        <v>79</v>
+      </c>
+      <c r="L33" t="s">
+        <v>27</v>
+      </c>
+      <c r="M33" t="s">
+        <v>266</v>
+      </c>
+      <c r="N33" t="s">
+        <v>21</v>
+      </c>
+      <c r="O33" t="s">
         <v>265</v>
       </c>
-      <c r="C33" t="s">
-        <v>32</v>
-      </c>
-      <c r="D33" t="s">
-        <v>33</v>
-      </c>
-      <c r="E33" t="s">
-        <v>34</v>
-      </c>
-      <c r="F33" t="s">
-        <v>266</v>
-      </c>
-      <c r="G33" t="s">
-        <v>267</v>
-      </c>
-      <c r="H33" t="s">
-        <v>21</v>
-      </c>
-      <c r="I33" t="s">
-        <v>21</v>
-      </c>
-      <c r="J33" t="s">
-        <v>270</v>
-      </c>
-      <c r="K33" t="s">
-        <v>88</v>
-      </c>
-      <c r="L33" t="s">
-        <v>89</v>
-      </c>
-      <c r="M33" t="s">
-        <v>271</v>
-      </c>
-      <c r="N33" t="s">
-        <v>21</v>
-      </c>
-      <c r="O33" t="s">
-        <v>268</v>
-      </c>
       <c r="P33" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="Q33" t="s">
-        <v>269</v>
+        <v>144</v>
       </c>
       <c r="R33" t="s">
         <v>21</v>
       </c>
       <c r="S33" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="T33" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="U33" t="s">
         <v>26</v>
@@ -3509,13 +3476,13 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="B34" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="C34" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="D34" t="s">
         <v>22</v>
@@ -3524,40 +3491,40 @@
         <v>23</v>
       </c>
       <c r="F34" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="G34" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="H34" t="s">
-        <v>94</v>
+        <v>271</v>
       </c>
       <c r="I34" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="J34" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="K34" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="L34" t="s">
         <v>27</v>
       </c>
       <c r="M34" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="N34" t="s">
         <v>21</v>
       </c>
       <c r="O34" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="P34" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="Q34" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="R34" t="s">
         <v>21</v>
@@ -3574,13 +3541,13 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="B35" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="C35" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="D35" t="s">
         <v>22</v>
@@ -3589,40 +3556,40 @@
         <v>23</v>
       </c>
       <c r="F35" t="s">
-        <v>151</v>
+        <v>277</v>
       </c>
       <c r="G35" t="s">
+        <v>36</v>
+      </c>
+      <c r="H35" t="s">
+        <v>150</v>
+      </c>
+      <c r="I35" t="s">
+        <v>165</v>
+      </c>
+      <c r="J35" t="s">
         <v>280</v>
       </c>
-      <c r="H35" t="s">
-        <v>281</v>
-      </c>
-      <c r="I35" t="s">
-        <v>173</v>
-      </c>
-      <c r="J35" t="s">
-        <v>283</v>
-      </c>
       <c r="K35" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="L35" t="s">
         <v>27</v>
       </c>
       <c r="M35" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="N35" t="s">
         <v>21</v>
       </c>
       <c r="O35" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="P35" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="Q35" t="s">
-        <v>154</v>
+        <v>279</v>
       </c>
       <c r="R35" t="s">
         <v>21</v>
@@ -3639,13 +3606,13 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="B36" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="C36" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="D36" t="s">
         <v>22</v>
@@ -3654,40 +3621,40 @@
         <v>23</v>
       </c>
       <c r="F36" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="G36" t="s">
-        <v>36</v>
+        <v>285</v>
       </c>
       <c r="H36" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="I36" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="J36" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="K36" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="L36" t="s">
         <v>27</v>
       </c>
       <c r="M36" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="N36" t="s">
         <v>21</v>
       </c>
       <c r="O36" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="P36" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="Q36" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="R36" t="s">
         <v>21</v>
@@ -3704,136 +3671,71 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B37" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C37" t="s">
-        <v>172</v>
+        <v>32</v>
       </c>
       <c r="D37" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="E37" t="s">
         <v>23</v>
       </c>
       <c r="F37" t="s">
+        <v>292</v>
+      </c>
+      <c r="G37" t="s">
+        <v>293</v>
+      </c>
+      <c r="H37" t="s">
         <v>294</v>
       </c>
-      <c r="G37" t="s">
-        <v>295</v>
-      </c>
-      <c r="H37" t="s">
-        <v>160</v>
-      </c>
       <c r="I37" t="s">
-        <v>175</v>
+        <v>21</v>
       </c>
       <c r="J37" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="K37" t="s">
-        <v>88</v>
+        <v>29</v>
       </c>
       <c r="L37" t="s">
         <v>27</v>
       </c>
       <c r="M37" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="N37" t="s">
         <v>21</v>
       </c>
       <c r="O37" t="s">
+        <v>295</v>
+      </c>
+      <c r="P37" t="s">
+        <v>295</v>
+      </c>
+      <c r="Q37" t="s">
         <v>296</v>
       </c>
-      <c r="P37" t="s">
-        <v>296</v>
-      </c>
-      <c r="Q37" t="s">
-        <v>297</v>
-      </c>
       <c r="R37" t="s">
         <v>21</v>
       </c>
       <c r="S37" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="T37" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="U37" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A38" t="s">
-        <v>300</v>
-      </c>
-      <c r="B38" t="s">
-        <v>301</v>
-      </c>
-      <c r="C38" t="s">
-        <v>32</v>
-      </c>
-      <c r="D38" t="s">
-        <v>33</v>
-      </c>
-      <c r="E38" t="s">
-        <v>23</v>
-      </c>
-      <c r="F38" t="s">
-        <v>302</v>
-      </c>
-      <c r="G38" t="s">
-        <v>303</v>
-      </c>
-      <c r="H38" t="s">
-        <v>304</v>
-      </c>
-      <c r="I38" t="s">
-        <v>21</v>
-      </c>
-      <c r="J38" t="s">
-        <v>307</v>
-      </c>
-      <c r="K38" t="s">
-        <v>29</v>
-      </c>
-      <c r="L38" t="s">
-        <v>27</v>
-      </c>
-      <c r="M38" t="s">
-        <v>308</v>
-      </c>
-      <c r="N38" t="s">
-        <v>21</v>
-      </c>
-      <c r="O38" t="s">
-        <v>305</v>
-      </c>
-      <c r="P38" t="s">
-        <v>305</v>
-      </c>
-      <c r="Q38" t="s">
-        <v>306</v>
-      </c>
-      <c r="R38" t="s">
-        <v>21</v>
-      </c>
-      <c r="S38" t="s">
-        <v>59</v>
-      </c>
-      <c r="T38" t="s">
-        <v>40</v>
-      </c>
-      <c r="U38" t="s">
-        <v>26</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:U38"/>
+  <autoFilter ref="A1:U37"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
